--- a/new original/EN/Data/chara_talk.xlsx
+++ b/new original/EN/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$127</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$132</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="282">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -83,6 +83,62 @@
   </si>
   <si>
     <t xml:space="preserve">hope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kiss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">*kiss*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">curse_wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">You homewrecker!
+Grrr!
+I’ll ruin everything!
+I won’t forgive you!
+I won’t accept this!
+Go to hell!
+Graaaargh!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">grats_wed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congratulations!
+Be happy!
+Woo-hoo!
+Wonderful!
+You’re a perfect match! 
+So lovey-dovey!
+Awesome!
+Here’s to love.
+Cheers.
+Kiss! Kiss!
+You did it!
+A beautiful day.
+You’re meant to be.
+Love is in the air!
+It’s like a fairy tale.
+To love!
+Drink up!
+Bravo!
+So precious...
+Stay close and happy.
+A perfect couple is born!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">die</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Die!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no_problem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No problem</t>
   </si>
   <si>
     <t xml:space="preserve">unlock_stairs_nasu</t>
@@ -1447,15 +1503,15 @@
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
       <charset val="128"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
       <charset val="128"/>
     </font>
   </fonts>
@@ -1526,15 +1582,15 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1582,9 +1638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2377440</xdr:colOff>
+      <xdr:colOff>2376360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1594,7 +1650,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50982120" cy="125640"/>
+          <a:ext cx="50981040" cy="124560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1627,9 +1683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>516960</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>64080</xdr:rowOff>
+      <xdr:colOff>515880</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>63000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1639,7 +1695,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55509840" cy="42085800"/>
+          <a:ext cx="55508760" cy="46324800"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1774,7 +1830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM128"/>
+  <dimension ref="A1:CM133"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -1987,7 +2043,7 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -2023,7 +2079,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2059,142 +2115,187 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-      <c r="S7" s="1"/>
-      <c r="T7" s="1"/>
-      <c r="AW7" s="1"/>
-    </row>
-    <row r="8" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U7" s="3"/>
+      <c r="V7" s="3"/>
+      <c r="W7" s="3"/>
+      <c r="X7" s="3"/>
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="3"/>
+      <c r="AA7" s="3"/>
+      <c r="AB7" s="3"/>
+      <c r="AC7" s="3"/>
+      <c r="AD7" s="3"/>
+      <c r="AE7" s="3"/>
+      <c r="AF7" s="3"/>
+      <c r="AG7" s="3"/>
+      <c r="AH7" s="3"/>
+      <c r="AI7" s="3"/>
+      <c r="AJ7" s="3"/>
+      <c r="AK7" s="3"/>
+      <c r="AL7" s="3"/>
+      <c r="AM7" s="3"/>
+      <c r="AN7" s="3"/>
+      <c r="AO7" s="3"/>
+      <c r="AP7" s="3"/>
+      <c r="AQ7" s="3"/>
+      <c r="AR7" s="3"/>
+      <c r="AS7" s="3"/>
+      <c r="AT7" s="3"/>
+      <c r="AU7" s="3"/>
+      <c r="AV7" s="3"/>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="AW8" s="1"/>
-    </row>
-    <row r="9" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U8" s="3"/>
+      <c r="V8" s="3"/>
+      <c r="W8" s="3"/>
+      <c r="X8" s="3"/>
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="3"/>
+      <c r="AA8" s="3"/>
+      <c r="AB8" s="3"/>
+      <c r="AC8" s="3"/>
+      <c r="AD8" s="3"/>
+      <c r="AE8" s="3"/>
+      <c r="AF8" s="3"/>
+      <c r="AG8" s="3"/>
+      <c r="AH8" s="3"/>
+      <c r="AI8" s="3"/>
+      <c r="AJ8" s="3"/>
+      <c r="AK8" s="3"/>
+      <c r="AL8" s="3"/>
+      <c r="AM8" s="3"/>
+      <c r="AN8" s="3"/>
+      <c r="AO8" s="3"/>
+      <c r="AP8" s="3"/>
+      <c r="AQ8" s="3"/>
+      <c r="AR8" s="3"/>
+      <c r="AS8" s="3"/>
+      <c r="AT8" s="3"/>
+      <c r="AU8" s="3"/>
+      <c r="AV8" s="3"/>
+    </row>
+    <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C9" s="1"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="AW9" s="1"/>
-    </row>
-    <row r="10" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U9" s="3"/>
+      <c r="V9" s="3"/>
+      <c r="W9" s="3"/>
+      <c r="X9" s="3"/>
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="3"/>
+      <c r="AA9" s="3"/>
+      <c r="AB9" s="3"/>
+      <c r="AC9" s="3"/>
+      <c r="AD9" s="3"/>
+      <c r="AE9" s="3"/>
+      <c r="AF9" s="3"/>
+      <c r="AG9" s="3"/>
+      <c r="AH9" s="3"/>
+      <c r="AI9" s="3"/>
+      <c r="AJ9" s="3"/>
+      <c r="AK9" s="3"/>
+      <c r="AL9" s="3"/>
+      <c r="AM9" s="3"/>
+      <c r="AN9" s="3"/>
+      <c r="AO9" s="3"/>
+      <c r="AP9" s="3"/>
+      <c r="AQ9" s="3"/>
+      <c r="AR9" s="3"/>
+      <c r="AS9" s="3"/>
+      <c r="AT9" s="3"/>
+      <c r="AU9" s="3"/>
+      <c r="AV9" s="3"/>
+    </row>
+    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="AW10" s="1"/>
-    </row>
-    <row r="11" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U10" s="3"/>
+      <c r="V10" s="3"/>
+      <c r="W10" s="3"/>
+      <c r="X10" s="3"/>
+      <c r="Y10" s="3"/>
+      <c r="Z10" s="3"/>
+      <c r="AA10" s="3"/>
+      <c r="AB10" s="3"/>
+      <c r="AC10" s="3"/>
+      <c r="AD10" s="3"/>
+      <c r="AE10" s="3"/>
+      <c r="AF10" s="3"/>
+      <c r="AG10" s="3"/>
+      <c r="AH10" s="3"/>
+      <c r="AI10" s="3"/>
+      <c r="AJ10" s="3"/>
+      <c r="AK10" s="3"/>
+      <c r="AL10" s="3"/>
+      <c r="AM10" s="3"/>
+      <c r="AN10" s="3"/>
+      <c r="AO10" s="3"/>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="3"/>
+      <c r="AT10" s="3"/>
+      <c r="AU10" s="3"/>
+      <c r="AV10" s="3"/>
+    </row>
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="1"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="AW11" s="1"/>
-    </row>
-    <row r="12" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+      <c r="W11" s="3"/>
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="3"/>
+      <c r="AA11" s="3"/>
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+      <c r="AF11" s="3"/>
+      <c r="AG11" s="3"/>
+      <c r="AH11" s="3"/>
+      <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
+      <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
+      <c r="AR11" s="3"/>
+      <c r="AS11" s="3"/>
+      <c r="AT11" s="3"/>
+      <c r="AU11" s="3"/>
+      <c r="AV11" s="3"/>
+    </row>
+    <row r="12" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
@@ -2221,198 +2322,148 @@
       <c r="T12" s="1"/>
       <c r="AW12" s="1"/>
     </row>
-    <row r="13" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3"/>
-      <c r="AS13" s="3"/>
-      <c r="AT13" s="3"/>
-      <c r="AU13" s="3"/>
-      <c r="AV13" s="3"/>
-    </row>
-    <row r="14" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="AW13" s="1"/>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="5"/>
-      <c r="U14" s="3"/>
-      <c r="V14" s="3"/>
-      <c r="W14" s="3"/>
-      <c r="X14" s="3"/>
-      <c r="Y14" s="3"/>
-      <c r="Z14" s="3"/>
-      <c r="AA14" s="3"/>
-      <c r="AB14" s="3"/>
-      <c r="AC14" s="3"/>
-      <c r="AD14" s="3"/>
-      <c r="AE14" s="3"/>
-      <c r="AF14" s="3"/>
-      <c r="AG14" s="3"/>
-      <c r="AH14" s="3"/>
-      <c r="AI14" s="3"/>
-      <c r="AJ14" s="3"/>
-      <c r="AK14" s="3"/>
-      <c r="AL14" s="3"/>
-      <c r="AM14" s="3"/>
-      <c r="AN14" s="3"/>
-      <c r="AO14" s="3"/>
-      <c r="AP14" s="3"/>
-      <c r="AQ14" s="3"/>
-      <c r="AR14" s="3"/>
-      <c r="AS14" s="3"/>
-      <c r="AT14" s="3"/>
-      <c r="AU14" s="3"/>
-      <c r="AV14" s="3"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
+      <c r="N14" s="1"/>
+      <c r="O14" s="1"/>
+      <c r="P14" s="1"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="1"/>
+      <c r="S14" s="1"/>
+      <c r="T14" s="1"/>
+      <c r="AW14" s="1"/>
+    </row>
+    <row r="15" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C15" s="5"/>
-      <c r="U15" s="3"/>
-      <c r="V15" s="3"/>
-      <c r="W15" s="3"/>
-      <c r="X15" s="3"/>
-      <c r="Y15" s="3"/>
-      <c r="Z15" s="3"/>
-      <c r="AA15" s="3"/>
-      <c r="AB15" s="3"/>
-      <c r="AC15" s="3"/>
-      <c r="AD15" s="3"/>
-      <c r="AE15" s="3"/>
-      <c r="AF15" s="3"/>
-      <c r="AG15" s="3"/>
-      <c r="AH15" s="3"/>
-      <c r="AI15" s="3"/>
-      <c r="AJ15" s="3"/>
-      <c r="AK15" s="3"/>
-      <c r="AL15" s="3"/>
-      <c r="AM15" s="3"/>
-      <c r="AN15" s="3"/>
-      <c r="AO15" s="3"/>
-      <c r="AP15" s="3"/>
-      <c r="AQ15" s="3"/>
-      <c r="AR15" s="3"/>
-      <c r="AS15" s="3"/>
-      <c r="AT15" s="3"/>
-      <c r="AU15" s="3"/>
-      <c r="AV15" s="3"/>
-    </row>
-    <row r="16" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1"/>
+      <c r="S15" s="1"/>
+      <c r="T15" s="1"/>
+      <c r="AW15" s="1"/>
+    </row>
+    <row r="16" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="U16" s="3"/>
-      <c r="V16" s="3"/>
-      <c r="W16" s="3"/>
-      <c r="X16" s="3"/>
-      <c r="Y16" s="3"/>
-      <c r="Z16" s="3"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="3"/>
-      <c r="AC16" s="3"/>
-      <c r="AD16" s="3"/>
-      <c r="AE16" s="3"/>
-      <c r="AF16" s="3"/>
-      <c r="AG16" s="3"/>
-      <c r="AH16" s="3"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="3"/>
-      <c r="AK16" s="3"/>
-      <c r="AL16" s="3"/>
-      <c r="AM16" s="3"/>
-      <c r="AN16" s="3"/>
-      <c r="AO16" s="3"/>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="3"/>
-      <c r="AR16" s="3"/>
-      <c r="AS16" s="3"/>
-      <c r="AT16" s="3"/>
-      <c r="AU16" s="3"/>
-      <c r="AV16" s="3"/>
-    </row>
-    <row r="17" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
+      <c r="M16" s="1"/>
+      <c r="N16" s="1"/>
+      <c r="O16" s="1"/>
+      <c r="P16" s="1"/>
+      <c r="Q16" s="1"/>
+      <c r="R16" s="1"/>
+      <c r="S16" s="1"/>
+      <c r="T16" s="1"/>
+      <c r="AW16" s="1"/>
+    </row>
+    <row r="17" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
       <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="U17" s="3"/>
-      <c r="V17" s="3"/>
-      <c r="W17" s="3"/>
-      <c r="X17" s="3"/>
-      <c r="Y17" s="3"/>
-      <c r="Z17" s="3"/>
-      <c r="AA17" s="3"/>
-      <c r="AB17" s="3"/>
-      <c r="AC17" s="3"/>
-      <c r="AD17" s="3"/>
-      <c r="AE17" s="3"/>
-      <c r="AF17" s="3"/>
-      <c r="AG17" s="3"/>
-      <c r="AH17" s="3"/>
-      <c r="AI17" s="3"/>
-      <c r="AJ17" s="3"/>
-      <c r="AK17" s="3"/>
-      <c r="AL17" s="3"/>
-      <c r="AM17" s="3"/>
-      <c r="AN17" s="3"/>
-      <c r="AO17" s="3"/>
-      <c r="AP17" s="3"/>
-      <c r="AQ17" s="3"/>
-      <c r="AR17" s="3"/>
-      <c r="AS17" s="3"/>
-      <c r="AT17" s="3"/>
-      <c r="AU17" s="3"/>
-      <c r="AV17" s="3"/>
-    </row>
-    <row r="18" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="1"/>
+      <c r="L17" s="1"/>
+      <c r="M17" s="1"/>
+      <c r="N17" s="1"/>
+      <c r="O17" s="1"/>
+      <c r="P17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
+      <c r="AW17" s="1"/>
+    </row>
+    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
       <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="5"/>
       <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3"/>
@@ -2449,6 +2500,7 @@
       <c r="B19" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="C19" s="5"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
@@ -2478,13 +2530,14 @@
       <c r="AU19" s="3"/>
       <c r="AV19" s="3"/>
     </row>
-    <row r="20" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="C20" s="5"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2514,14 +2567,14 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="6"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2551,13 +2604,14 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="C22" s="5"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2587,7 +2641,7 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
@@ -2624,7 +2678,7 @@
       <c r="AU23" s="3"/>
       <c r="AV23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
         <v>60</v>
       </c>
@@ -2660,11 +2714,11 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="7" t="s">
         <v>63</v>
       </c>
       <c r="U25" s="3"/>
@@ -2696,13 +2750,14 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>65</v>
       </c>
+      <c r="C26" s="7"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2768,11 +2823,11 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="5" t="s">
         <v>69</v>
       </c>
       <c r="C28" s="5"/>
@@ -2805,7 +2860,7 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
@@ -2841,7 +2896,7 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>72</v>
       </c>
@@ -2877,12 +2932,12 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>73</v>
+      <c r="B31" s="7" t="s">
+        <v>75</v>
       </c>
       <c r="U31" s="3"/>
       <c r="V31" s="3"/>
@@ -2913,12 +2968,12 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="U32" s="3"/>
       <c r="V32" s="3"/>
@@ -2949,13 +3004,14 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B33" s="5" t="s">
         <v>78</v>
       </c>
+      <c r="B33" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -2985,12 +3041,12 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B34" s="1" t="s">
         <v>80</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>81</v>
       </c>
       <c r="U34" s="3"/>
       <c r="V34" s="3"/>
@@ -3021,12 +3077,12 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
@@ -3057,12 +3113,12 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B36" s="5" t="s">
         <v>83</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>84</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3093,7 +3149,7 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
         <v>85</v>
       </c>
@@ -3129,7 +3185,7 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
         <v>87</v>
       </c>
@@ -3165,11 +3221,11 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="U39" s="3"/>
@@ -3201,7 +3257,7 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
@@ -3237,14 +3293,13 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="5"/>
       <c r="U41" s="3"/>
       <c r="V41" s="3"/>
       <c r="W41" s="3"/>
@@ -3274,11 +3329,11 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="5" t="s">
         <v>96</v>
       </c>
       <c r="U42" s="3"/>
@@ -3310,7 +3365,7 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>97</v>
       </c>
@@ -3346,7 +3401,7 @@
       <c r="AU43" s="3"/>
       <c r="AV43" s="3"/>
     </row>
-    <row r="44" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
         <v>99</v>
       </c>
@@ -3382,31 +3437,13 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="7" t="s">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="7" t="s">
+      <c r="B45" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="C45" s="7"/>
-      <c r="D45" s="7"/>
-      <c r="E45" s="7"/>
-      <c r="F45" s="7"/>
-      <c r="G45" s="7"/>
-      <c r="H45" s="7"/>
-      <c r="I45" s="7"/>
-      <c r="J45" s="7"/>
-      <c r="K45" s="7"/>
-      <c r="L45" s="7"/>
-      <c r="M45" s="7"/>
-      <c r="N45" s="7"/>
-      <c r="O45" s="7"/>
-      <c r="P45" s="7"/>
-      <c r="Q45" s="7"/>
-      <c r="R45" s="7"/>
-      <c r="S45" s="7"/>
-      <c r="T45" s="7"/>
       <c r="U45" s="3"/>
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
@@ -3436,31 +3473,14 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="7" t="s">
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
         <v>103</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="7"/>
-      <c r="G46" s="7"/>
-      <c r="H46" s="7"/>
-      <c r="I46" s="7"/>
-      <c r="J46" s="7"/>
-      <c r="K46" s="7"/>
-      <c r="L46" s="7"/>
-      <c r="M46" s="7"/>
-      <c r="N46" s="7"/>
-      <c r="O46" s="7"/>
-      <c r="P46" s="7"/>
-      <c r="Q46" s="7"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="7"/>
-      <c r="T46" s="7"/>
+      <c r="C46" s="5"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3490,31 +3510,13 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="7" t="s">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="C47" s="7"/>
-      <c r="D47" s="7"/>
-      <c r="E47" s="7"/>
-      <c r="F47" s="7"/>
-      <c r="G47" s="7"/>
-      <c r="H47" s="7"/>
-      <c r="I47" s="7"/>
-      <c r="J47" s="7"/>
-      <c r="K47" s="7"/>
-      <c r="L47" s="7"/>
-      <c r="M47" s="7"/>
-      <c r="N47" s="7"/>
-      <c r="O47" s="7"/>
-      <c r="P47" s="7"/>
-      <c r="Q47" s="7"/>
-      <c r="R47" s="7"/>
-      <c r="S47" s="7"/>
-      <c r="T47" s="7"/>
       <c r="U47" s="3"/>
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
@@ -3544,31 +3546,13 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="7" t="s">
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="1" t="s">
         <v>107</v>
       </c>
       <c r="B48" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-      <c r="M48" s="7"/>
-      <c r="N48" s="7"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3598,31 +3582,13 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="7" t="s">
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
         <v>109</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C49" s="7"/>
-      <c r="D49" s="7"/>
-      <c r="E49" s="7"/>
-      <c r="F49" s="7"/>
-      <c r="G49" s="7"/>
-      <c r="H49" s="7"/>
-      <c r="I49" s="7"/>
-      <c r="J49" s="7"/>
-      <c r="K49" s="7"/>
-      <c r="L49" s="7"/>
-      <c r="M49" s="7"/>
-      <c r="N49" s="7"/>
-      <c r="O49" s="7"/>
-      <c r="P49" s="7"/>
-      <c r="Q49" s="7"/>
-      <c r="R49" s="7"/>
-      <c r="S49" s="7"/>
-      <c r="T49" s="7"/>
       <c r="U49" s="3"/>
       <c r="V49" s="3"/>
       <c r="W49" s="3"/>
@@ -3652,31 +3618,31 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="7" t="s">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="7"/>
-      <c r="D50" s="7"/>
-      <c r="E50" s="7"/>
-      <c r="F50" s="7"/>
-      <c r="G50" s="7"/>
-      <c r="H50" s="7"/>
-      <c r="I50" s="7"/>
-      <c r="J50" s="7"/>
-      <c r="K50" s="7"/>
-      <c r="L50" s="7"/>
-      <c r="M50" s="7"/>
-      <c r="N50" s="7"/>
-      <c r="O50" s="7"/>
-      <c r="P50" s="7"/>
-      <c r="Q50" s="7"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="7"/>
-      <c r="T50" s="7"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8"/>
+      <c r="S50" s="8"/>
+      <c r="T50" s="8"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -3706,31 +3672,31 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="7" t="s">
+    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="7"/>
-      <c r="D51" s="7"/>
-      <c r="E51" s="7"/>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="7"/>
-      <c r="I51" s="7"/>
-      <c r="J51" s="7"/>
-      <c r="K51" s="7"/>
-      <c r="L51" s="7"/>
-      <c r="M51" s="7"/>
-      <c r="N51" s="7"/>
-      <c r="O51" s="7"/>
-      <c r="P51" s="7"/>
-      <c r="Q51" s="7"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="7"/>
-      <c r="T51" s="7"/>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="8"/>
+      <c r="S51" s="8"/>
+      <c r="T51" s="8"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -3760,31 +3726,31 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="7" t="s">
+    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="8" t="s">
         <v>115</v>
       </c>
       <c r="B52" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="7"/>
-      <c r="E52" s="7"/>
-      <c r="F52" s="7"/>
-      <c r="G52" s="7"/>
-      <c r="H52" s="7"/>
-      <c r="I52" s="7"/>
-      <c r="J52" s="7"/>
-      <c r="K52" s="7"/>
-      <c r="L52" s="7"/>
-      <c r="M52" s="7"/>
-      <c r="N52" s="7"/>
-      <c r="O52" s="7"/>
-      <c r="P52" s="7"/>
-      <c r="Q52" s="7"/>
-      <c r="R52" s="7"/>
-      <c r="S52" s="7"/>
-      <c r="T52" s="7"/>
+      <c r="C52" s="8"/>
+      <c r="D52" s="8"/>
+      <c r="E52" s="8"/>
+      <c r="F52" s="8"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="8"/>
+      <c r="I52" s="8"/>
+      <c r="J52" s="8"/>
+      <c r="K52" s="8"/>
+      <c r="L52" s="8"/>
+      <c r="M52" s="8"/>
+      <c r="N52" s="8"/>
+      <c r="O52" s="8"/>
+      <c r="P52" s="8"/>
+      <c r="Q52" s="8"/>
+      <c r="R52" s="8"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="8"/>
       <c r="U52" s="3"/>
       <c r="V52" s="3"/>
       <c r="W52" s="3"/>
@@ -3814,13 +3780,31 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
+    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="5" t="s">
         <v>118</v>
       </c>
+      <c r="C53" s="8"/>
+      <c r="D53" s="8"/>
+      <c r="E53" s="8"/>
+      <c r="F53" s="8"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="8"/>
+      <c r="I53" s="8"/>
+      <c r="J53" s="8"/>
+      <c r="K53" s="8"/>
+      <c r="L53" s="8"/>
+      <c r="M53" s="8"/>
+      <c r="N53" s="8"/>
+      <c r="O53" s="8"/>
+      <c r="P53" s="8"/>
+      <c r="Q53" s="8"/>
+      <c r="R53" s="8"/>
+      <c r="S53" s="8"/>
+      <c r="T53" s="8"/>
       <c r="U53" s="3"/>
       <c r="V53" s="3"/>
       <c r="W53" s="3"/>
@@ -3850,13 +3834,31 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="1" t="s">
+    <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="5" t="s">
         <v>120</v>
       </c>
+      <c r="C54" s="8"/>
+      <c r="D54" s="8"/>
+      <c r="E54" s="8"/>
+      <c r="F54" s="8"/>
+      <c r="G54" s="8"/>
+      <c r="H54" s="8"/>
+      <c r="I54" s="8"/>
+      <c r="J54" s="8"/>
+      <c r="K54" s="8"/>
+      <c r="L54" s="8"/>
+      <c r="M54" s="8"/>
+      <c r="N54" s="8"/>
+      <c r="O54" s="8"/>
+      <c r="P54" s="8"/>
+      <c r="Q54" s="8"/>
+      <c r="R54" s="8"/>
+      <c r="S54" s="8"/>
+      <c r="T54" s="8"/>
       <c r="U54" s="3"/>
       <c r="V54" s="3"/>
       <c r="W54" s="3"/>
@@ -3886,13 +3888,31 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
+    <row r="55" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="5" t="s">
         <v>122</v>
       </c>
+      <c r="C55" s="8"/>
+      <c r="D55" s="8"/>
+      <c r="E55" s="8"/>
+      <c r="F55" s="8"/>
+      <c r="G55" s="8"/>
+      <c r="H55" s="8"/>
+      <c r="I55" s="8"/>
+      <c r="J55" s="8"/>
+      <c r="K55" s="8"/>
+      <c r="L55" s="8"/>
+      <c r="M55" s="8"/>
+      <c r="N55" s="8"/>
+      <c r="O55" s="8"/>
+      <c r="P55" s="8"/>
+      <c r="Q55" s="8"/>
+      <c r="R55" s="8"/>
+      <c r="S55" s="8"/>
+      <c r="T55" s="8"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
@@ -3923,12 +3943,30 @@
       <c r="AV55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="1" t="s">
+      <c r="A56" s="8" t="s">
         <v>123</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C56" s="8"/>
+      <c r="D56" s="8"/>
+      <c r="E56" s="8"/>
+      <c r="F56" s="8"/>
+      <c r="G56" s="8"/>
+      <c r="H56" s="8"/>
+      <c r="I56" s="8"/>
+      <c r="J56" s="8"/>
+      <c r="K56" s="8"/>
+      <c r="L56" s="8"/>
+      <c r="M56" s="8"/>
+      <c r="N56" s="8"/>
+      <c r="O56" s="8"/>
+      <c r="P56" s="8"/>
+      <c r="Q56" s="8"/>
+      <c r="R56" s="8"/>
+      <c r="S56" s="8"/>
+      <c r="T56" s="8"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
@@ -3958,13 +3996,31 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="B57" s="1" t="s">
+    <row r="57" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="8" t="s">
         <v>125</v>
       </c>
+      <c r="B57" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="5"/>
+      <c r="D57" s="8"/>
+      <c r="E57" s="8"/>
+      <c r="F57" s="8"/>
+      <c r="G57" s="8"/>
+      <c r="H57" s="8"/>
+      <c r="I57" s="8"/>
+      <c r="J57" s="8"/>
+      <c r="K57" s="8"/>
+      <c r="L57" s="8"/>
+      <c r="M57" s="8"/>
+      <c r="N57" s="8"/>
+      <c r="O57" s="8"/>
+      <c r="P57" s="8"/>
+      <c r="Q57" s="8"/>
+      <c r="R57" s="8"/>
+      <c r="S57" s="8"/>
+      <c r="T57" s="8"/>
       <c r="U57" s="3"/>
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
@@ -3994,12 +4050,12 @@
       <c r="AU57" s="3"/>
       <c r="AV57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B58" s="5" t="s">
         <v>127</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>128</v>
       </c>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
@@ -4032,10 +4088,10 @@
     </row>
     <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
@@ -4066,12 +4122,12 @@
       <c r="AU59" s="3"/>
       <c r="AV59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="B60" s="5" t="s">
         <v>131</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U60" s="3"/>
       <c r="V60" s="3"/>
@@ -4104,10 +4160,10 @@
     </row>
     <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B61" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>122</v>
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
@@ -4140,10 +4196,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -4174,12 +4230,12 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>122</v>
+        <v>136</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>137</v>
       </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
@@ -4210,12 +4266,12 @@
       <c r="AU63" s="3"/>
       <c r="AV63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="B64" s="5" t="s">
-        <v>136</v>
+        <v>138</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>139</v>
       </c>
       <c r="U64" s="3"/>
       <c r="V64" s="3"/>
@@ -4246,9 +4302,12 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>141</v>
       </c>
       <c r="U65" s="3"/>
       <c r="V65" s="3"/>
@@ -4279,12 +4338,12 @@
       <c r="AU65" s="3"/>
       <c r="AV65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="66" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="B66" s="5" t="s">
-        <v>139</v>
+        <v>142</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -4317,10 +4376,10 @@
     </row>
     <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>141</v>
+        <v>132</v>
       </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
@@ -4350,54 +4409,13 @@
       <c r="AT67" s="3"/>
       <c r="AU67" s="3"/>
       <c r="AV67" s="3"/>
-      <c r="AY67" s="3"/>
-      <c r="AZ67" s="3"/>
-      <c r="BA67" s="3"/>
-      <c r="BB67" s="3"/>
-      <c r="BC67" s="3"/>
-      <c r="BD67" s="3"/>
-      <c r="BE67" s="3"/>
-      <c r="BF67" s="3"/>
-      <c r="BG67" s="3"/>
-      <c r="BH67" s="3"/>
-      <c r="BI67" s="3"/>
-      <c r="BJ67" s="3"/>
-      <c r="BK67" s="3"/>
-      <c r="BL67" s="3"/>
-      <c r="BM67" s="3"/>
-      <c r="BN67" s="3"/>
-      <c r="BO67" s="3"/>
-      <c r="BP67" s="3"/>
-      <c r="BQ67" s="3"/>
-      <c r="BR67" s="3"/>
-      <c r="BS67" s="3"/>
-      <c r="BT67" s="3"/>
-      <c r="BU67" s="3"/>
-      <c r="BV67" s="3"/>
-      <c r="BW67" s="3"/>
-      <c r="BX67" s="3"/>
-      <c r="BY67" s="3"/>
-      <c r="BZ67" s="3"/>
-      <c r="CA67" s="3"/>
-      <c r="CB67" s="3"/>
-      <c r="CC67" s="3"/>
-      <c r="CD67" s="3"/>
-      <c r="CE67" s="3"/>
-      <c r="CF67" s="3"/>
-      <c r="CG67" s="3"/>
-      <c r="CH67" s="3"/>
-      <c r="CI67" s="3"/>
-      <c r="CJ67" s="3"/>
-      <c r="CK67" s="3"/>
-      <c r="CL67" s="3"/>
-      <c r="CM67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -4427,54 +4445,13 @@
       <c r="AT68" s="3"/>
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
-      <c r="AY68" s="3"/>
-      <c r="AZ68" s="3"/>
-      <c r="BA68" s="3"/>
-      <c r="BB68" s="3"/>
-      <c r="BC68" s="3"/>
-      <c r="BD68" s="3"/>
-      <c r="BE68" s="3"/>
-      <c r="BF68" s="3"/>
-      <c r="BG68" s="3"/>
-      <c r="BH68" s="3"/>
-      <c r="BI68" s="3"/>
-      <c r="BJ68" s="3"/>
-      <c r="BK68" s="3"/>
-      <c r="BL68" s="3"/>
-      <c r="BM68" s="3"/>
-      <c r="BN68" s="3"/>
-      <c r="BO68" s="3"/>
-      <c r="BP68" s="3"/>
-      <c r="BQ68" s="3"/>
-      <c r="BR68" s="3"/>
-      <c r="BS68" s="3"/>
-      <c r="BT68" s="3"/>
-      <c r="BU68" s="3"/>
-      <c r="BV68" s="3"/>
-      <c r="BW68" s="3"/>
-      <c r="BX68" s="3"/>
-      <c r="BY68" s="3"/>
-      <c r="BZ68" s="3"/>
-      <c r="CA68" s="3"/>
-      <c r="CB68" s="3"/>
-      <c r="CC68" s="3"/>
-      <c r="CD68" s="3"/>
-      <c r="CE68" s="3"/>
-      <c r="CF68" s="3"/>
-      <c r="CG68" s="3"/>
-      <c r="CH68" s="3"/>
-      <c r="CI68" s="3"/>
-      <c r="CJ68" s="3"/>
-      <c r="CK68" s="3"/>
-      <c r="CL68" s="3"/>
-      <c r="CM68" s="3"/>
-    </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B69" s="1" t="s">
         <v>145</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
@@ -4504,53 +4481,9 @@
       <c r="AT69" s="3"/>
       <c r="AU69" s="3"/>
       <c r="AV69" s="3"/>
-      <c r="AY69" s="3"/>
-      <c r="AZ69" s="3"/>
-      <c r="BA69" s="3"/>
-      <c r="BB69" s="3"/>
-      <c r="BC69" s="3"/>
-      <c r="BD69" s="3"/>
-      <c r="BE69" s="3"/>
-      <c r="BF69" s="3"/>
-      <c r="BG69" s="3"/>
-      <c r="BH69" s="3"/>
-      <c r="BI69" s="3"/>
-      <c r="BJ69" s="3"/>
-      <c r="BK69" s="3"/>
-      <c r="BL69" s="3"/>
-      <c r="BM69" s="3"/>
-      <c r="BN69" s="3"/>
-      <c r="BO69" s="3"/>
-      <c r="BP69" s="3"/>
-      <c r="BQ69" s="3"/>
-      <c r="BR69" s="3"/>
-      <c r="BS69" s="3"/>
-      <c r="BT69" s="3"/>
-      <c r="BU69" s="3"/>
-      <c r="BV69" s="3"/>
-      <c r="BW69" s="3"/>
-      <c r="BX69" s="3"/>
-      <c r="BY69" s="3"/>
-      <c r="BZ69" s="3"/>
-      <c r="CA69" s="3"/>
-      <c r="CB69" s="3"/>
-      <c r="CC69" s="3"/>
-      <c r="CD69" s="3"/>
-      <c r="CE69" s="3"/>
-      <c r="CF69" s="3"/>
-      <c r="CG69" s="3"/>
-      <c r="CH69" s="3"/>
-      <c r="CI69" s="3"/>
-      <c r="CJ69" s="3"/>
-      <c r="CK69" s="3"/>
-      <c r="CL69" s="3"/>
-      <c r="CM69" s="3"/>
-    </row>
-    <row r="70" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="B70" s="5" t="s">
         <v>147</v>
       </c>
       <c r="U70" s="3"/>
@@ -4581,49 +4514,8 @@
       <c r="AT70" s="3"/>
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
-      <c r="AY70" s="3"/>
-      <c r="AZ70" s="3"/>
-      <c r="BA70" s="3"/>
-      <c r="BB70" s="3"/>
-      <c r="BC70" s="3"/>
-      <c r="BD70" s="3"/>
-      <c r="BE70" s="3"/>
-      <c r="BF70" s="3"/>
-      <c r="BG70" s="3"/>
-      <c r="BH70" s="3"/>
-      <c r="BI70" s="3"/>
-      <c r="BJ70" s="3"/>
-      <c r="BK70" s="3"/>
-      <c r="BL70" s="3"/>
-      <c r="BM70" s="3"/>
-      <c r="BN70" s="3"/>
-      <c r="BO70" s="3"/>
-      <c r="BP70" s="3"/>
-      <c r="BQ70" s="3"/>
-      <c r="BR70" s="3"/>
-      <c r="BS70" s="3"/>
-      <c r="BT70" s="3"/>
-      <c r="BU70" s="3"/>
-      <c r="BV70" s="3"/>
-      <c r="BW70" s="3"/>
-      <c r="BX70" s="3"/>
-      <c r="BY70" s="3"/>
-      <c r="BZ70" s="3"/>
-      <c r="CA70" s="3"/>
-      <c r="CB70" s="3"/>
-      <c r="CC70" s="3"/>
-      <c r="CD70" s="3"/>
-      <c r="CE70" s="3"/>
-      <c r="CF70" s="3"/>
-      <c r="CG70" s="3"/>
-      <c r="CH70" s="3"/>
-      <c r="CI70" s="3"/>
-      <c r="CJ70" s="3"/>
-      <c r="CK70" s="3"/>
-      <c r="CL70" s="3"/>
-      <c r="CM70" s="3"/>
-    </row>
-    <row r="71" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="71" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
         <v>148</v>
       </c>
@@ -4658,53 +4550,12 @@
       <c r="AT71" s="3"/>
       <c r="AU71" s="3"/>
       <c r="AV71" s="3"/>
-      <c r="AY71" s="3"/>
-      <c r="AZ71" s="3"/>
-      <c r="BA71" s="3"/>
-      <c r="BB71" s="3"/>
-      <c r="BC71" s="3"/>
-      <c r="BD71" s="3"/>
-      <c r="BE71" s="3"/>
-      <c r="BF71" s="3"/>
-      <c r="BG71" s="3"/>
-      <c r="BH71" s="3"/>
-      <c r="BI71" s="3"/>
-      <c r="BJ71" s="3"/>
-      <c r="BK71" s="3"/>
-      <c r="BL71" s="3"/>
-      <c r="BM71" s="3"/>
-      <c r="BN71" s="3"/>
-      <c r="BO71" s="3"/>
-      <c r="BP71" s="3"/>
-      <c r="BQ71" s="3"/>
-      <c r="BR71" s="3"/>
-      <c r="BS71" s="3"/>
-      <c r="BT71" s="3"/>
-      <c r="BU71" s="3"/>
-      <c r="BV71" s="3"/>
-      <c r="BW71" s="3"/>
-      <c r="BX71" s="3"/>
-      <c r="BY71" s="3"/>
-      <c r="BZ71" s="3"/>
-      <c r="CA71" s="3"/>
-      <c r="CB71" s="3"/>
-      <c r="CC71" s="3"/>
-      <c r="CD71" s="3"/>
-      <c r="CE71" s="3"/>
-      <c r="CF71" s="3"/>
-      <c r="CG71" s="3"/>
-      <c r="CH71" s="3"/>
-      <c r="CI71" s="3"/>
-      <c r="CJ71" s="3"/>
-      <c r="CK71" s="3"/>
-      <c r="CL71" s="3"/>
-      <c r="CM71" s="3"/>
-    </row>
-    <row r="72" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
         <v>150</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="1" t="s">
         <v>151</v>
       </c>
       <c r="U72" s="3"/>
@@ -4777,11 +4628,11 @@
       <c r="CL72" s="3"/>
       <c r="CM72" s="3"/>
     </row>
-    <row r="73" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="U73" s="3"/>
@@ -4854,11 +4705,11 @@
       <c r="CL73" s="3"/>
       <c r="CM73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="1" t="s">
         <v>155</v>
       </c>
       <c r="U74" s="3"/>
@@ -4931,11 +4782,11 @@
       <c r="CL74" s="3"/>
       <c r="CM74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="5" t="s">
         <v>157</v>
       </c>
       <c r="U75" s="3"/>
@@ -5008,7 +4859,7 @@
       <c r="CL75" s="3"/>
       <c r="CM75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>158</v>
       </c>
@@ -5085,12 +4936,12 @@
       <c r="CL76" s="3"/>
       <c r="CM76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="1" t="s">
-        <v>122</v>
+      <c r="B77" s="5" t="s">
+        <v>161</v>
       </c>
       <c r="U77" s="3"/>
       <c r="V77" s="3"/>
@@ -5162,12 +5013,12 @@
       <c r="CL77" s="3"/>
       <c r="CM77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>161</v>
-      </c>
-      <c r="B78" s="1" t="s">
-        <v>122</v>
+        <v>162</v>
+      </c>
+      <c r="B78" s="5" t="s">
+        <v>163</v>
       </c>
       <c r="U78" s="3"/>
       <c r="V78" s="3"/>
@@ -5239,12 +5090,12 @@
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>122</v>
+        <v>164</v>
+      </c>
+      <c r="B79" s="5" t="s">
+        <v>165</v>
       </c>
       <c r="U79" s="3"/>
       <c r="V79" s="3"/>
@@ -5318,10 +5169,10 @@
     </row>
     <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>122</v>
+        <v>167</v>
       </c>
       <c r="U80" s="3"/>
       <c r="V80" s="3"/>
@@ -5393,12 +5244,12 @@
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="B81" s="1" t="s">
-        <v>122</v>
+        <v>168</v>
+      </c>
+      <c r="B81" s="5" t="s">
+        <v>169</v>
       </c>
       <c r="U81" s="3"/>
       <c r="V81" s="3"/>
@@ -5472,10 +5323,10 @@
     </row>
     <row r="82" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
@@ -5547,12 +5398,12 @@
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="B83" s="5" t="s">
-        <v>167</v>
+        <v>171</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
@@ -5626,10 +5477,10 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>169</v>
+        <v>132</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
@@ -5701,12 +5552,12 @@
       <c r="CL84" s="3"/>
       <c r="CM84" s="3"/>
     </row>
-    <row r="85" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="B85" s="5" t="s">
-        <v>171</v>
+        <v>173</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
@@ -5780,11 +5631,39 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>173</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="U86" s="3"/>
+      <c r="V86" s="3"/>
+      <c r="W86" s="3"/>
+      <c r="X86" s="3"/>
+      <c r="Y86" s="3"/>
+      <c r="Z86" s="3"/>
+      <c r="AA86" s="3"/>
+      <c r="AB86" s="3"/>
+      <c r="AC86" s="3"/>
+      <c r="AD86" s="3"/>
+      <c r="AE86" s="3"/>
+      <c r="AF86" s="3"/>
+      <c r="AG86" s="3"/>
+      <c r="AH86" s="3"/>
+      <c r="AI86" s="3"/>
+      <c r="AJ86" s="3"/>
+      <c r="AK86" s="3"/>
+      <c r="AL86" s="3"/>
+      <c r="AM86" s="3"/>
+      <c r="AN86" s="3"/>
+      <c r="AO86" s="3"/>
+      <c r="AP86" s="3"/>
+      <c r="AQ86" s="3"/>
+      <c r="AR86" s="3"/>
+      <c r="AS86" s="3"/>
+      <c r="AT86" s="3"/>
+      <c r="AU86" s="3"/>
+      <c r="AV86" s="3"/>
       <c r="AY86" s="3"/>
       <c r="AZ86" s="3"/>
       <c r="BA86" s="3"/>
@@ -5829,11 +5708,39 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>132</v>
+      </c>
+      <c r="U87" s="3"/>
+      <c r="V87" s="3"/>
+      <c r="W87" s="3"/>
+      <c r="X87" s="3"/>
+      <c r="Y87" s="3"/>
+      <c r="Z87" s="3"/>
+      <c r="AA87" s="3"/>
+      <c r="AB87" s="3"/>
+      <c r="AC87" s="3"/>
+      <c r="AD87" s="3"/>
+      <c r="AE87" s="3"/>
+      <c r="AF87" s="3"/>
+      <c r="AG87" s="3"/>
+      <c r="AH87" s="3"/>
+      <c r="AI87" s="3"/>
+      <c r="AJ87" s="3"/>
+      <c r="AK87" s="3"/>
+      <c r="AL87" s="3"/>
+      <c r="AM87" s="3"/>
+      <c r="AN87" s="3"/>
+      <c r="AO87" s="3"/>
+      <c r="AP87" s="3"/>
+      <c r="AQ87" s="3"/>
+      <c r="AR87" s="3"/>
+      <c r="AS87" s="3"/>
+      <c r="AT87" s="3"/>
+      <c r="AU87" s="3"/>
+      <c r="AV87" s="3"/>
       <c r="AY87" s="3"/>
       <c r="AZ87" s="3"/>
       <c r="BA87" s="3"/>
@@ -5876,10 +5783,41 @@
       <c r="CL87" s="3"/>
       <c r="CM87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A88" s="5" t="s">
-        <v>175</v>
-      </c>
+    <row r="88" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="U88" s="3"/>
+      <c r="V88" s="3"/>
+      <c r="W88" s="3"/>
+      <c r="X88" s="3"/>
+      <c r="Y88" s="3"/>
+      <c r="Z88" s="3"/>
+      <c r="AA88" s="3"/>
+      <c r="AB88" s="3"/>
+      <c r="AC88" s="3"/>
+      <c r="AD88" s="3"/>
+      <c r="AE88" s="3"/>
+      <c r="AF88" s="3"/>
+      <c r="AG88" s="3"/>
+      <c r="AH88" s="3"/>
+      <c r="AI88" s="3"/>
+      <c r="AJ88" s="3"/>
+      <c r="AK88" s="3"/>
+      <c r="AL88" s="3"/>
+      <c r="AM88" s="3"/>
+      <c r="AN88" s="3"/>
+      <c r="AO88" s="3"/>
+      <c r="AP88" s="3"/>
+      <c r="AQ88" s="3"/>
+      <c r="AR88" s="3"/>
+      <c r="AS88" s="3"/>
+      <c r="AT88" s="3"/>
+      <c r="AU88" s="3"/>
+      <c r="AV88" s="3"/>
       <c r="AY88" s="3"/>
       <c r="AZ88" s="3"/>
       <c r="BA88" s="3"/>
@@ -5922,13 +5860,41 @@
       <c r="CL88" s="3"/>
       <c r="CM88" s="3"/>
     </row>
-    <row r="89" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B89" s="5" t="s">
-        <v>177</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="U89" s="3"/>
+      <c r="V89" s="3"/>
+      <c r="W89" s="3"/>
+      <c r="X89" s="3"/>
+      <c r="Y89" s="3"/>
+      <c r="Z89" s="3"/>
+      <c r="AA89" s="3"/>
+      <c r="AB89" s="3"/>
+      <c r="AC89" s="3"/>
+      <c r="AD89" s="3"/>
+      <c r="AE89" s="3"/>
+      <c r="AF89" s="3"/>
+      <c r="AG89" s="3"/>
+      <c r="AH89" s="3"/>
+      <c r="AI89" s="3"/>
+      <c r="AJ89" s="3"/>
+      <c r="AK89" s="3"/>
+      <c r="AL89" s="3"/>
+      <c r="AM89" s="3"/>
+      <c r="AN89" s="3"/>
+      <c r="AO89" s="3"/>
+      <c r="AP89" s="3"/>
+      <c r="AQ89" s="3"/>
+      <c r="AR89" s="3"/>
+      <c r="AS89" s="3"/>
+      <c r="AT89" s="3"/>
+      <c r="AU89" s="3"/>
+      <c r="AV89" s="3"/>
       <c r="AY89" s="3"/>
       <c r="AZ89" s="3"/>
       <c r="BA89" s="3"/>
@@ -5971,13 +5937,41 @@
       <c r="CL89" s="3"/>
       <c r="CM89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B90" s="1" t="s">
-        <v>122</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="B90" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+      <c r="W90" s="3"/>
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+      <c r="Z90" s="3"/>
+      <c r="AA90" s="3"/>
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+      <c r="AF90" s="3"/>
+      <c r="AG90" s="3"/>
+      <c r="AH90" s="3"/>
+      <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
+      <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
+      <c r="AR90" s="3"/>
+      <c r="AS90" s="3"/>
+      <c r="AT90" s="3"/>
+      <c r="AU90" s="3"/>
+      <c r="AV90" s="3"/>
       <c r="AY90" s="3"/>
       <c r="AZ90" s="3"/>
       <c r="BA90" s="3"/>
@@ -6020,12 +6014,12 @@
       <c r="CL90" s="3"/>
       <c r="CM90" s="3"/>
     </row>
-    <row r="91" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="91" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="B91" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
@@ -6069,31 +6063,13 @@
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A92" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="B92" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="C92" s="7"/>
-      <c r="D92" s="7"/>
-      <c r="E92" s="7"/>
-      <c r="F92" s="7"/>
-      <c r="G92" s="7"/>
-      <c r="H92" s="7"/>
-      <c r="I92" s="7"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7"/>
-      <c r="S92" s="7"/>
-      <c r="T92" s="7"/>
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="AY92" s="3"/>
       <c r="AZ92" s="3"/>
       <c r="BA92" s="3"/>
@@ -6136,12 +6112,9 @@
       <c r="CL92" s="3"/>
       <c r="CM92" s="3"/>
     </row>
-    <row r="93" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="B93" s="5" t="s">
-        <v>184</v>
+    <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="AY93" s="3"/>
       <c r="AZ93" s="3"/>
@@ -6185,12 +6158,12 @@
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
@@ -6234,61 +6207,54 @@
       <c r="CL94" s="3"/>
       <c r="CM94" s="3"/>
     </row>
-    <row r="95" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="B95" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
-      <c r="N95" s="1"/>
-      <c r="O95" s="1"/>
-      <c r="P95" s="1"/>
-      <c r="Q95" s="1"/>
-      <c r="R95" s="1"/>
-      <c r="S95" s="1"/>
-      <c r="T95" s="1"/>
-      <c r="U95" s="1"/>
-      <c r="V95" s="1"/>
-      <c r="W95" s="1"/>
-      <c r="X95" s="1"/>
-      <c r="Y95" s="1"/>
-      <c r="Z95" s="1"/>
-      <c r="AA95" s="1"/>
-      <c r="AB95" s="1"/>
-      <c r="AC95" s="1"/>
-      <c r="AD95" s="1"/>
-      <c r="AE95" s="1"/>
-      <c r="AF95" s="1"/>
-      <c r="AG95" s="1"/>
-      <c r="AH95" s="1"/>
-      <c r="AI95" s="1"/>
-      <c r="AJ95" s="1"/>
-      <c r="AK95" s="1"/>
-      <c r="AL95" s="1"/>
-      <c r="AM95" s="1"/>
-      <c r="AN95" s="1"/>
-      <c r="AO95" s="1"/>
-      <c r="AP95" s="1"/>
-      <c r="AQ95" s="1"/>
-      <c r="AR95" s="1"/>
-      <c r="AS95" s="1"/>
-      <c r="AT95" s="1"/>
-      <c r="AU95" s="1"/>
-      <c r="AV95" s="1"/>
-      <c r="AW95" s="1"/>
-      <c r="AX95" s="1"/>
+      <c r="B95" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AY95" s="3"/>
+      <c r="AZ95" s="3"/>
+      <c r="BA95" s="3"/>
+      <c r="BB95" s="3"/>
+      <c r="BC95" s="3"/>
+      <c r="BD95" s="3"/>
+      <c r="BE95" s="3"/>
+      <c r="BF95" s="3"/>
+      <c r="BG95" s="3"/>
+      <c r="BH95" s="3"/>
+      <c r="BI95" s="3"/>
+      <c r="BJ95" s="3"/>
+      <c r="BK95" s="3"/>
+      <c r="BL95" s="3"/>
+      <c r="BM95" s="3"/>
+      <c r="BN95" s="3"/>
+      <c r="BO95" s="3"/>
+      <c r="BP95" s="3"/>
+      <c r="BQ95" s="3"/>
+      <c r="BR95" s="3"/>
+      <c r="BS95" s="3"/>
+      <c r="BT95" s="3"/>
+      <c r="BU95" s="3"/>
+      <c r="BV95" s="3"/>
+      <c r="BW95" s="3"/>
+      <c r="BX95" s="3"/>
+      <c r="BY95" s="3"/>
+      <c r="BZ95" s="3"/>
+      <c r="CA95" s="3"/>
+      <c r="CB95" s="3"/>
+      <c r="CC95" s="3"/>
+      <c r="CD95" s="3"/>
+      <c r="CE95" s="3"/>
+      <c r="CF95" s="3"/>
+      <c r="CG95" s="3"/>
+      <c r="CH95" s="3"/>
+      <c r="CI95" s="3"/>
+      <c r="CJ95" s="3"/>
+      <c r="CK95" s="3"/>
+      <c r="CL95" s="3"/>
+      <c r="CM95" s="3"/>
     </row>
     <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
@@ -6339,13 +6305,31 @@
       <c r="CL96" s="3"/>
       <c r="CM96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+    <row r="97" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="s">
         <v>191</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>192</v>
       </c>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="8"/>
+      <c r="S97" s="8"/>
+      <c r="T97" s="8"/>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
       <c r="BA97" s="3"/>
@@ -6395,58 +6379,152 @@
       <c r="B98" s="5" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="99" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY98" s="3"/>
+      <c r="AZ98" s="3"/>
+      <c r="BA98" s="3"/>
+      <c r="BB98" s="3"/>
+      <c r="BC98" s="3"/>
+      <c r="BD98" s="3"/>
+      <c r="BE98" s="3"/>
+      <c r="BF98" s="3"/>
+      <c r="BG98" s="3"/>
+      <c r="BH98" s="3"/>
+      <c r="BI98" s="3"/>
+      <c r="BJ98" s="3"/>
+      <c r="BK98" s="3"/>
+      <c r="BL98" s="3"/>
+      <c r="BM98" s="3"/>
+      <c r="BN98" s="3"/>
+      <c r="BO98" s="3"/>
+      <c r="BP98" s="3"/>
+      <c r="BQ98" s="3"/>
+      <c r="BR98" s="3"/>
+      <c r="BS98" s="3"/>
+      <c r="BT98" s="3"/>
+      <c r="BU98" s="3"/>
+      <c r="BV98" s="3"/>
+      <c r="BW98" s="3"/>
+      <c r="BX98" s="3"/>
+      <c r="BY98" s="3"/>
+      <c r="BZ98" s="3"/>
+      <c r="CA98" s="3"/>
+      <c r="CB98" s="3"/>
+      <c r="CC98" s="3"/>
+      <c r="CD98" s="3"/>
+      <c r="CE98" s="3"/>
+      <c r="CF98" s="3"/>
+      <c r="CG98" s="3"/>
+      <c r="CH98" s="3"/>
+      <c r="CI98" s="3"/>
+      <c r="CJ98" s="3"/>
+      <c r="CK98" s="3"/>
+      <c r="CL98" s="3"/>
+      <c r="CM98" s="3"/>
+    </row>
+    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="1" t="s">
         <v>195</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="5"/>
-      <c r="D99" s="5"/>
-      <c r="E99" s="5"/>
-      <c r="F99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
-      <c r="J99" s="5"/>
-      <c r="K99" s="5"/>
-      <c r="L99" s="5"/>
-      <c r="M99" s="5"/>
-      <c r="N99" s="5"/>
-      <c r="O99" s="5"/>
-      <c r="P99" s="5"/>
-      <c r="Q99" s="5"/>
-      <c r="R99" s="5"/>
-      <c r="S99" s="5"/>
-      <c r="T99" s="5"/>
-    </row>
-    <row r="100" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="8" t="s">
+      <c r="AY99" s="3"/>
+      <c r="AZ99" s="3"/>
+      <c r="BA99" s="3"/>
+      <c r="BB99" s="3"/>
+      <c r="BC99" s="3"/>
+      <c r="BD99" s="3"/>
+      <c r="BE99" s="3"/>
+      <c r="BF99" s="3"/>
+      <c r="BG99" s="3"/>
+      <c r="BH99" s="3"/>
+      <c r="BI99" s="3"/>
+      <c r="BJ99" s="3"/>
+      <c r="BK99" s="3"/>
+      <c r="BL99" s="3"/>
+      <c r="BM99" s="3"/>
+      <c r="BN99" s="3"/>
+      <c r="BO99" s="3"/>
+      <c r="BP99" s="3"/>
+      <c r="BQ99" s="3"/>
+      <c r="BR99" s="3"/>
+      <c r="BS99" s="3"/>
+      <c r="BT99" s="3"/>
+      <c r="BU99" s="3"/>
+      <c r="BV99" s="3"/>
+      <c r="BW99" s="3"/>
+      <c r="BX99" s="3"/>
+      <c r="BY99" s="3"/>
+      <c r="BZ99" s="3"/>
+      <c r="CA99" s="3"/>
+      <c r="CB99" s="3"/>
+      <c r="CC99" s="3"/>
+      <c r="CD99" s="3"/>
+      <c r="CE99" s="3"/>
+      <c r="CF99" s="3"/>
+      <c r="CG99" s="3"/>
+      <c r="CH99" s="3"/>
+      <c r="CI99" s="3"/>
+      <c r="CJ99" s="3"/>
+      <c r="CK99" s="3"/>
+      <c r="CL99" s="3"/>
+      <c r="CM99" s="3"/>
+    </row>
+    <row r="100" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="1" t="s">
         <v>197</v>
       </c>
       <c r="B100" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="5"/>
-      <c r="D100" s="5"/>
-      <c r="E100" s="5"/>
-      <c r="F100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
-      <c r="J100" s="5"/>
-      <c r="K100" s="5"/>
-      <c r="L100" s="5"/>
-      <c r="M100" s="5"/>
-      <c r="N100" s="5"/>
-      <c r="O100" s="5"/>
-      <c r="P100" s="5"/>
-      <c r="Q100" s="5"/>
-      <c r="R100" s="5"/>
-      <c r="S100" s="5"/>
-      <c r="T100" s="5"/>
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
+      <c r="Z100" s="1"/>
+      <c r="AA100" s="1"/>
+      <c r="AB100" s="1"/>
+      <c r="AC100" s="1"/>
+      <c r="AD100" s="1"/>
+      <c r="AE100" s="1"/>
+      <c r="AF100" s="1"/>
+      <c r="AG100" s="1"/>
+      <c r="AH100" s="1"/>
+      <c r="AI100" s="1"/>
+      <c r="AJ100" s="1"/>
+      <c r="AK100" s="1"/>
+      <c r="AL100" s="1"/>
+      <c r="AM100" s="1"/>
+      <c r="AN100" s="1"/>
+      <c r="AO100" s="1"/>
+      <c r="AP100" s="1"/>
+      <c r="AQ100" s="1"/>
+      <c r="AR100" s="1"/>
+      <c r="AS100" s="1"/>
+      <c r="AT100" s="1"/>
+      <c r="AU100" s="1"/>
+      <c r="AV100" s="1"/>
+      <c r="AW100" s="1"/>
+      <c r="AX100" s="1"/>
     </row>
     <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
@@ -6455,55 +6533,137 @@
       <c r="B101" s="5" t="s">
         <v>200</v>
       </c>
-      <c r="C101" s="5"/>
-      <c r="D101" s="5"/>
-      <c r="E101" s="5"/>
-      <c r="F101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
-      <c r="J101" s="5"/>
-      <c r="K101" s="5"/>
-      <c r="L101" s="5"/>
-      <c r="M101" s="5"/>
-      <c r="N101" s="5"/>
-      <c r="O101" s="5"/>
-      <c r="P101" s="5"/>
-      <c r="Q101" s="5"/>
-      <c r="R101" s="5"/>
-      <c r="S101" s="5"/>
-      <c r="T101" s="5"/>
-    </row>
-    <row r="102" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY101" s="3"/>
+      <c r="AZ101" s="3"/>
+      <c r="BA101" s="3"/>
+      <c r="BB101" s="3"/>
+      <c r="BC101" s="3"/>
+      <c r="BD101" s="3"/>
+      <c r="BE101" s="3"/>
+      <c r="BF101" s="3"/>
+      <c r="BG101" s="3"/>
+      <c r="BH101" s="3"/>
+      <c r="BI101" s="3"/>
+      <c r="BJ101" s="3"/>
+      <c r="BK101" s="3"/>
+      <c r="BL101" s="3"/>
+      <c r="BM101" s="3"/>
+      <c r="BN101" s="3"/>
+      <c r="BO101" s="3"/>
+      <c r="BP101" s="3"/>
+      <c r="BQ101" s="3"/>
+      <c r="BR101" s="3"/>
+      <c r="BS101" s="3"/>
+      <c r="BT101" s="3"/>
+      <c r="BU101" s="3"/>
+      <c r="BV101" s="3"/>
+      <c r="BW101" s="3"/>
+      <c r="BX101" s="3"/>
+      <c r="BY101" s="3"/>
+      <c r="BZ101" s="3"/>
+      <c r="CA101" s="3"/>
+      <c r="CB101" s="3"/>
+      <c r="CC101" s="3"/>
+      <c r="CD101" s="3"/>
+      <c r="CE101" s="3"/>
+      <c r="CF101" s="3"/>
+      <c r="CG101" s="3"/>
+      <c r="CH101" s="3"/>
+      <c r="CI101" s="3"/>
+      <c r="CJ101" s="3"/>
+      <c r="CK101" s="3"/>
+      <c r="CL101" s="3"/>
+      <c r="CM101" s="3"/>
+    </row>
+    <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="AY102" s="3"/>
+      <c r="AZ102" s="3"/>
+      <c r="BA102" s="3"/>
+      <c r="BB102" s="3"/>
+      <c r="BC102" s="3"/>
+      <c r="BD102" s="3"/>
+      <c r="BE102" s="3"/>
+      <c r="BF102" s="3"/>
+      <c r="BG102" s="3"/>
+      <c r="BH102" s="3"/>
+      <c r="BI102" s="3"/>
+      <c r="BJ102" s="3"/>
+      <c r="BK102" s="3"/>
+      <c r="BL102" s="3"/>
+      <c r="BM102" s="3"/>
+      <c r="BN102" s="3"/>
+      <c r="BO102" s="3"/>
+      <c r="BP102" s="3"/>
+      <c r="BQ102" s="3"/>
+      <c r="BR102" s="3"/>
+      <c r="BS102" s="3"/>
+      <c r="BT102" s="3"/>
+      <c r="BU102" s="3"/>
+      <c r="BV102" s="3"/>
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+      <c r="BY102" s="3"/>
+      <c r="BZ102" s="3"/>
+      <c r="CA102" s="3"/>
+      <c r="CB102" s="3"/>
+      <c r="CC102" s="3"/>
+      <c r="CD102" s="3"/>
+      <c r="CE102" s="3"/>
+      <c r="CF102" s="3"/>
+      <c r="CG102" s="3"/>
+      <c r="CH102" s="3"/>
+      <c r="CI102" s="3"/>
+      <c r="CJ102" s="3"/>
+      <c r="CK102" s="3"/>
+      <c r="CL102" s="3"/>
+      <c r="CM102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="104" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="105" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
         <v>206</v>
       </c>
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
+      <c r="S104" s="5"/>
+      <c r="T104" s="5"/>
+    </row>
+    <row r="105" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
+        <v>207</v>
+      </c>
       <c r="B105" s="5" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C105" s="5"/>
       <c r="D105" s="5"/>
@@ -6524,12 +6684,12 @@
       <c r="S105" s="5"/>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C106" s="5"/>
       <c r="D106" s="5"/>
@@ -6550,127 +6710,145 @@
       <c r="S106" s="5"/>
       <c r="T106" s="5"/>
     </row>
-    <row r="107" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="1" t="s">
-        <v>210</v>
-      </c>
-      <c r="B107" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="B107" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="D107" s="5" t="s">
+      <c r="B108" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="E107" s="5" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="F107" s="5" t="s">
+      <c r="B109" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="G107" s="5" t="s">
+    </row>
+    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="H107" s="5" t="s">
+      <c r="B110" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="I107" s="5" t="s">
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+    </row>
+    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="J107" s="5" t="s">
+      <c r="B111" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="K107" s="5" t="s">
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+      <c r="S111" s="5"/>
+      <c r="T111" s="5"/>
+    </row>
+    <row r="112" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="L107" s="5" t="s">
+      <c r="B112" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="M107" s="5" t="s">
+      <c r="C112" s="5" t="s">
         <v>222</v>
       </c>
-      <c r="N107" s="5" t="s">
+      <c r="D112" s="5" t="s">
         <v>223</v>
       </c>
-      <c r="O107" s="5" t="s">
+      <c r="E112" s="5" t="s">
         <v>224</v>
       </c>
-      <c r="P107" s="5" t="s">
+      <c r="F112" s="5" t="s">
         <v>225</v>
       </c>
-      <c r="Q107" s="5" t="s">
+      <c r="G112" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="R107" s="5" t="s">
+      <c r="H112" s="5" t="s">
         <v>227</v>
       </c>
-      <c r="S107" s="5" t="s">
+      <c r="I112" s="5" t="s">
         <v>228</v>
       </c>
-      <c r="T107" s="5" t="s">
+      <c r="J112" s="5" t="s">
         <v>229</v>
       </c>
-    </row>
-    <row r="108" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="K112" s="5" t="s">
         <v>230</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="L112" s="5" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="M112" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="B109" s="5" t="s">
+      <c r="N112" s="5" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A110" s="7" t="s">
+      <c r="O112" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="P112" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="C110" s="7"/>
-      <c r="D110" s="7"/>
-      <c r="E110" s="7"/>
-      <c r="F110" s="7"/>
-      <c r="G110" s="7"/>
-      <c r="H110" s="7"/>
-      <c r="I110" s="7"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="7"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="7"/>
-      <c r="S110" s="7"/>
-      <c r="T110" s="7"/>
-    </row>
-    <row r="111" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A111" s="1" t="s">
+      <c r="Q112" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="B111" s="9" t="s">
+      <c r="R112" s="5" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A112" s="1" t="s">
+      <c r="S112" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="B112" s="9" t="s">
+      <c r="T112" s="5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="113" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="113" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
         <v>240</v>
       </c>
@@ -6678,109 +6856,127 @@
         <v>241</v>
       </c>
     </row>
-    <row r="114" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="114" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
         <v>242</v>
       </c>
-      <c r="B114" s="1" t="s">
+      <c r="B114" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="C114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="E114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="F114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="G114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="H114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="I114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="J114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="K114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="L114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="M114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="N114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="O114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="P114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="R114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="S114" s="1" t="s">
-        <v>243</v>
-      </c>
-      <c r="T114" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="115" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    </row>
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8" t="s">
         <v>244</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="8"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="8"/>
+      <c r="S115" s="8"/>
+      <c r="T115" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="9" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="117" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B117" s="1" t="s">
+      <c r="B117" s="9" t="s">
         <v>249</v>
       </c>
     </row>
-    <row r="118" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="118" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B118" s="1" t="s">
+      <c r="B118" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="5" t="s">
+      <c r="B119" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="P119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="S119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>254</v>
       </c>
@@ -6796,23 +6992,23 @@
         <v>257</v>
       </c>
     </row>
-    <row r="122" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B122" s="5" t="s">
+      <c r="B122" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B123" s="5" t="s">
+      <c r="B123" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>262</v>
       </c>
@@ -6820,7 +7016,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>264</v>
       </c>
@@ -6828,23 +7024,23 @@
         <v>265</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B126" s="9" t="s">
+      <c r="B126" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B127" s="9" t="s">
+      <c r="B127" s="5" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>270</v>
       </c>
@@ -6852,8 +7048,48 @@
         <v>271</v>
       </c>
     </row>
+    <row r="129" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="1" t="s">
+        <v>272</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="B130" s="5" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B131" s="9" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="B132" s="9" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="B133" s="5" t="s">
+        <v>281</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T127"/>
+  <autoFilter ref="A2:T132"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/new original/EN/Data/chara_talk.xlsx
+++ b/new original/EN/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$132</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$134</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="286">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -83,6 +83,37 @@
   </si>
   <si>
     <t xml:space="preserve">hope</t>
+  </si>
+  <si>
+    <t xml:space="preserve">play_baby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mommy!
+Mama!
+Baba!
+Baba baba!
+Waaah!
+Where’s Mommy?
+Are you Mommy?
+…Mommy?
+…Mommy! </t>
+  </si>
+  <si>
+    <t xml:space="preserve">play_mama</t>
+  </si>
+  <si>
+    <t xml:space="preserve">There, there.
+Mommy’s here~
+Good boy, good boy.
+There, there.
+Mommy’s here.
+Mm-hmm, mm-hmm.
+It’s okay, it’s okay.
+Big hug!
+Hug.
+Mommy’s right here.
+Go on, you can be needy.
+I’ll take it all in.</t>
   </si>
   <si>
     <t xml:space="preserve">kiss</t>
@@ -1574,12 +1605,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1638,9 +1669,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2376360</xdr:colOff>
+      <xdr:colOff>2376000</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>124560</xdr:rowOff>
+      <xdr:rowOff>124200</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1650,7 +1681,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50981040" cy="124560"/>
+          <a:ext cx="50980680" cy="124200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1683,9 +1714,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>515880</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>63000</xdr:rowOff>
+      <xdr:colOff>515520</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>62640</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1695,7 +1726,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55508760" cy="46324800"/>
+          <a:ext cx="55508400" cy="49148280"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1830,7 +1861,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM133"/>
+  <dimension ref="A1:CM135"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2007,7 +2038,7 @@
       <c r="AU3" s="3"/>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -2043,11 +2074,11 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="U5" s="3"/>
@@ -2079,7 +2110,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2115,11 +2146,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="4" t="s">
         <v>27</v>
       </c>
       <c r="U7" s="3"/>
@@ -2151,11 +2182,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="4" t="s">
         <v>29</v>
       </c>
       <c r="U8" s="3"/>
@@ -2191,7 +2222,7 @@
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>31</v>
       </c>
       <c r="U9" s="3"/>
@@ -2223,11 +2254,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>33</v>
       </c>
       <c r="U10" s="3"/>
@@ -2259,11 +2290,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="6" t="s">
         <v>35</v>
       </c>
       <c r="U11" s="3"/>
@@ -2295,65 +2326,83 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="1"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="AW12" s="1"/>
-    </row>
-    <row r="13" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U12" s="3"/>
+      <c r="V12" s="3"/>
+      <c r="W12" s="3"/>
+      <c r="X12" s="3"/>
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="3"/>
+      <c r="AA12" s="3"/>
+      <c r="AB12" s="3"/>
+      <c r="AC12" s="3"/>
+      <c r="AD12" s="3"/>
+      <c r="AE12" s="3"/>
+      <c r="AF12" s="3"/>
+      <c r="AG12" s="3"/>
+      <c r="AH12" s="3"/>
+      <c r="AI12" s="3"/>
+      <c r="AJ12" s="3"/>
+      <c r="AK12" s="3"/>
+      <c r="AL12" s="3"/>
+      <c r="AM12" s="3"/>
+      <c r="AN12" s="3"/>
+      <c r="AO12" s="3"/>
+      <c r="AP12" s="3"/>
+      <c r="AQ12" s="3"/>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3"/>
+      <c r="AT12" s="3"/>
+      <c r="AU12" s="3"/>
+      <c r="AV12" s="3"/>
+    </row>
+    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="AW13" s="1"/>
-    </row>
-    <row r="14" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U13" s="3"/>
+      <c r="V13" s="3"/>
+      <c r="W13" s="3"/>
+      <c r="X13" s="3"/>
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="3"/>
+      <c r="AA13" s="3"/>
+      <c r="AB13" s="3"/>
+      <c r="AC13" s="3"/>
+      <c r="AD13" s="3"/>
+      <c r="AE13" s="3"/>
+      <c r="AF13" s="3"/>
+      <c r="AG13" s="3"/>
+      <c r="AH13" s="3"/>
+      <c r="AI13" s="3"/>
+      <c r="AJ13" s="3"/>
+      <c r="AK13" s="3"/>
+      <c r="AL13" s="3"/>
+      <c r="AM13" s="3"/>
+      <c r="AN13" s="3"/>
+      <c r="AO13" s="3"/>
+      <c r="AP13" s="3"/>
+      <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3"/>
+      <c r="AT13" s="3"/>
+      <c r="AU13" s="3"/>
+      <c r="AV13" s="3"/>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="1"/>
@@ -2376,11 +2425,11 @@
       <c r="T14" s="1"/>
       <c r="AW14" s="1"/>
     </row>
-    <row r="15" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="4" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="1"/>
@@ -2403,11 +2452,11 @@
       <c r="T15" s="1"/>
       <c r="AW15" s="1"/>
     </row>
-    <row r="16" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="1"/>
@@ -2430,11 +2479,11 @@
       <c r="T16" s="1"/>
       <c r="AW16" s="1"/>
     </row>
-    <row r="17" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="1"/>
@@ -2457,87 +2506,67 @@
       <c r="T17" s="1"/>
       <c r="AW17" s="1"/>
     </row>
-    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="U18" s="3"/>
-      <c r="V18" s="3"/>
-      <c r="W18" s="3"/>
-      <c r="X18" s="3"/>
-      <c r="Y18" s="3"/>
-      <c r="Z18" s="3"/>
-      <c r="AA18" s="3"/>
-      <c r="AB18" s="3"/>
-      <c r="AC18" s="3"/>
-      <c r="AD18" s="3"/>
-      <c r="AE18" s="3"/>
-      <c r="AF18" s="3"/>
-      <c r="AG18" s="3"/>
-      <c r="AH18" s="3"/>
-      <c r="AI18" s="3"/>
-      <c r="AJ18" s="3"/>
-      <c r="AK18" s="3"/>
-      <c r="AL18" s="3"/>
-      <c r="AM18" s="3"/>
-      <c r="AN18" s="3"/>
-      <c r="AO18" s="3"/>
-      <c r="AP18" s="3"/>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-      <c r="AS18" s="3"/>
-      <c r="AT18" s="3"/>
-      <c r="AU18" s="3"/>
-      <c r="AV18" s="3"/>
-    </row>
-    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="1"/>
+      <c r="L18" s="1"/>
+      <c r="M18" s="1"/>
+      <c r="N18" s="1"/>
+      <c r="O18" s="1"/>
+      <c r="P18" s="1"/>
+      <c r="Q18" s="1"/>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
+      <c r="AW18" s="1"/>
+    </row>
+    <row r="19" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
-      <c r="W19" s="3"/>
-      <c r="X19" s="3"/>
-      <c r="Y19" s="3"/>
-      <c r="Z19" s="3"/>
-      <c r="AA19" s="3"/>
-      <c r="AB19" s="3"/>
-      <c r="AC19" s="3"/>
-      <c r="AD19" s="3"/>
-      <c r="AE19" s="3"/>
-      <c r="AF19" s="3"/>
-      <c r="AG19" s="3"/>
-      <c r="AH19" s="3"/>
-      <c r="AI19" s="3"/>
-      <c r="AJ19" s="3"/>
-      <c r="AK19" s="3"/>
-      <c r="AL19" s="3"/>
-      <c r="AM19" s="3"/>
-      <c r="AN19" s="3"/>
-      <c r="AO19" s="3"/>
-      <c r="AP19" s="3"/>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
-      <c r="AS19" s="3"/>
-      <c r="AT19" s="3"/>
-      <c r="AU19" s="3"/>
-      <c r="AV19" s="3"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="5" t="s">
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="1"/>
+      <c r="L19" s="1"/>
+      <c r="M19" s="1"/>
+      <c r="N19" s="1"/>
+      <c r="O19" s="1"/>
+      <c r="P19" s="1"/>
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1"/>
+      <c r="AW19" s="1"/>
+    </row>
+    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C20" s="5"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2567,14 +2596,14 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="5"/>
+      <c r="C21" s="4"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2604,14 +2633,14 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="5"/>
+      <c r="C22" s="4"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2641,14 +2670,14 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="s">
+    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="5"/>
+      <c r="C23" s="4"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2679,12 +2708,13 @@
       <c r="AV23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="s">
+      <c r="A24" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>61</v>
       </c>
+      <c r="C24" s="4"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2714,13 +2744,14 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="7" t="s">
+      <c r="B25" s="4" t="s">
         <v>63</v>
       </c>
+      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2750,14 +2781,13 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="7" t="s">
+      <c r="B26" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C26" s="7"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2787,11 +2817,11 @@
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>67</v>
       </c>
       <c r="U27" s="3"/>
@@ -2823,14 +2853,14 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="5"/>
+      <c r="C28" s="7"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2860,11 +2890,11 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="4" t="s">
         <v>71</v>
       </c>
       <c r="U29" s="3"/>
@@ -2896,13 +2926,14 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="5" t="s">
+      <c r="B30" s="4" t="s">
         <v>73</v>
       </c>
+      <c r="C30" s="4"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2932,11 +2963,11 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="7" t="s">
+      <c r="B31" s="4" t="s">
         <v>75</v>
       </c>
       <c r="U31" s="3"/>
@@ -2968,11 +2999,11 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>77</v>
       </c>
       <c r="U32" s="3"/>
@@ -3004,14 +3035,13 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="5"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3041,11 +3071,11 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="U34" s="3"/>
@@ -3077,13 +3107,14 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="5" t="s">
+      <c r="B35" s="1" t="s">
         <v>83</v>
       </c>
+      <c r="C35" s="4"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3113,12 +3144,12 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>83</v>
+      <c r="B36" s="4" t="s">
+        <v>85</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3149,12 +3180,12 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="B37" s="5" t="s">
         <v>86</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>87</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -3185,12 +3216,12 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B38" s="4" t="s">
         <v>87</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>88</v>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3221,11 +3252,11 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="4" t="s">
         <v>90</v>
       </c>
       <c r="U39" s="3"/>
@@ -3257,11 +3288,11 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="5" t="s">
+      <c r="B40" s="4" t="s">
         <v>92</v>
       </c>
       <c r="U40" s="3"/>
@@ -3293,11 +3324,11 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="5" t="s">
+      <c r="B41" s="1" t="s">
         <v>94</v>
       </c>
       <c r="U41" s="3"/>
@@ -3329,11 +3360,11 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="4" t="s">
         <v>96</v>
       </c>
       <c r="U42" s="3"/>
@@ -3365,11 +3396,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="5" t="s">
+      <c r="B43" s="4" t="s">
         <v>98</v>
       </c>
       <c r="U43" s="3"/>
@@ -3405,7 +3436,7 @@
       <c r="A44" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="5" t="s">
+      <c r="B44" s="4" t="s">
         <v>100</v>
       </c>
       <c r="U44" s="3"/>
@@ -3437,11 +3468,11 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="5" t="s">
+      <c r="B45" s="4" t="s">
         <v>102</v>
       </c>
       <c r="U45" s="3"/>
@@ -3473,14 +3504,13 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C46" s="5"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3510,11 +3540,11 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="4" t="s">
         <v>106</v>
       </c>
       <c r="U47" s="3"/>
@@ -3546,13 +3576,14 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>108</v>
       </c>
+      <c r="C48" s="4"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3582,11 +3613,11 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="5" t="s">
+      <c r="B49" s="1" t="s">
         <v>110</v>
       </c>
       <c r="U49" s="3"/>
@@ -3618,31 +3649,13 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="8" t="s">
+    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="8" t="s">
+      <c r="B50" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="8"/>
-      <c r="H50" s="8"/>
-      <c r="I50" s="8"/>
-      <c r="J50" s="8"/>
-      <c r="K50" s="8"/>
-      <c r="L50" s="8"/>
-      <c r="M50" s="8"/>
-      <c r="N50" s="8"/>
-      <c r="O50" s="8"/>
-      <c r="P50" s="8"/>
-      <c r="Q50" s="8"/>
-      <c r="R50" s="8"/>
-      <c r="S50" s="8"/>
-      <c r="T50" s="8"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -3672,31 +3685,13 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="8" t="s">
+    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C51" s="8"/>
-      <c r="D51" s="8"/>
-      <c r="E51" s="8"/>
-      <c r="F51" s="8"/>
-      <c r="G51" s="8"/>
-      <c r="H51" s="8"/>
-      <c r="I51" s="8"/>
-      <c r="J51" s="8"/>
-      <c r="K51" s="8"/>
-      <c r="L51" s="8"/>
-      <c r="M51" s="8"/>
-      <c r="N51" s="8"/>
-      <c r="O51" s="8"/>
-      <c r="P51" s="8"/>
-      <c r="Q51" s="8"/>
-      <c r="R51" s="8"/>
-      <c r="S51" s="8"/>
-      <c r="T51" s="8"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -3726,11 +3721,11 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="8" t="s">
         <v>116</v>
       </c>
       <c r="C52" s="8"/>
@@ -3780,11 +3775,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>118</v>
       </c>
       <c r="C53" s="8"/>
@@ -3834,11 +3829,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C54" s="8"/>
@@ -3888,11 +3883,11 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>122</v>
       </c>
       <c r="C55" s="8"/>
@@ -3942,11 +3937,11 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="4" t="s">
         <v>124</v>
       </c>
       <c r="C56" s="8"/>
@@ -3996,14 +3991,14 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C57" s="5"/>
+      <c r="C57" s="8"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -4051,12 +4046,30 @@
       <c r="AV57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="1" t="s">
+      <c r="A58" s="8" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>128</v>
       </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="8"/>
+      <c r="E58" s="8"/>
+      <c r="F58" s="8"/>
+      <c r="G58" s="8"/>
+      <c r="H58" s="8"/>
+      <c r="I58" s="8"/>
+      <c r="J58" s="8"/>
+      <c r="K58" s="8"/>
+      <c r="L58" s="8"/>
+      <c r="M58" s="8"/>
+      <c r="N58" s="8"/>
+      <c r="O58" s="8"/>
+      <c r="P58" s="8"/>
+      <c r="Q58" s="8"/>
+      <c r="R58" s="8"/>
+      <c r="S58" s="8"/>
+      <c r="T58" s="8"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4086,13 +4099,31 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="1" t="s">
+    <row r="59" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="4" t="s">
         <v>130</v>
       </c>
+      <c r="C59" s="4"/>
+      <c r="D59" s="8"/>
+      <c r="E59" s="8"/>
+      <c r="F59" s="8"/>
+      <c r="G59" s="8"/>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
+      <c r="J59" s="8"/>
+      <c r="K59" s="8"/>
+      <c r="L59" s="8"/>
+      <c r="M59" s="8"/>
+      <c r="N59" s="8"/>
+      <c r="O59" s="8"/>
+      <c r="P59" s="8"/>
+      <c r="Q59" s="8"/>
+      <c r="R59" s="8"/>
+      <c r="S59" s="8"/>
+      <c r="T59" s="8"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -4163,7 +4194,7 @@
         <v>133</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
@@ -4196,10 +4227,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -4230,12 +4261,12 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B63" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="B63" s="5" t="s">
-        <v>137</v>
       </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
@@ -4302,11 +4333,11 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B65" s="4" t="s">
         <v>141</v>
       </c>
       <c r="U65" s="3"/>
@@ -4343,7 +4374,7 @@
         <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -4374,12 +4405,12 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" s="1" t="s">
-        <v>132</v>
+        <v>144</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>145</v>
       </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
@@ -4412,10 +4443,10 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -4446,12 +4477,12 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B69" s="5" t="s">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
@@ -4484,7 +4515,10 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -4515,12 +4549,12 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B71" s="5" t="s">
         <v>149</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>150</v>
       </c>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
@@ -4553,9 +4587,6 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="B72" s="1" t="s">
         <v>151</v>
       </c>
       <c r="U72" s="3"/>
@@ -4586,53 +4617,12 @@
       <c r="AT72" s="3"/>
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
-      <c r="AY72" s="3"/>
-      <c r="AZ72" s="3"/>
-      <c r="BA72" s="3"/>
-      <c r="BB72" s="3"/>
-      <c r="BC72" s="3"/>
-      <c r="BD72" s="3"/>
-      <c r="BE72" s="3"/>
-      <c r="BF72" s="3"/>
-      <c r="BG72" s="3"/>
-      <c r="BH72" s="3"/>
-      <c r="BI72" s="3"/>
-      <c r="BJ72" s="3"/>
-      <c r="BK72" s="3"/>
-      <c r="BL72" s="3"/>
-      <c r="BM72" s="3"/>
-      <c r="BN72" s="3"/>
-      <c r="BO72" s="3"/>
-      <c r="BP72" s="3"/>
-      <c r="BQ72" s="3"/>
-      <c r="BR72" s="3"/>
-      <c r="BS72" s="3"/>
-      <c r="BT72" s="3"/>
-      <c r="BU72" s="3"/>
-      <c r="BV72" s="3"/>
-      <c r="BW72" s="3"/>
-      <c r="BX72" s="3"/>
-      <c r="BY72" s="3"/>
-      <c r="BZ72" s="3"/>
-      <c r="CA72" s="3"/>
-      <c r="CB72" s="3"/>
-      <c r="CC72" s="3"/>
-      <c r="CD72" s="3"/>
-      <c r="CE72" s="3"/>
-      <c r="CF72" s="3"/>
-      <c r="CG72" s="3"/>
-      <c r="CH72" s="3"/>
-      <c r="CI72" s="3"/>
-      <c r="CJ72" s="3"/>
-      <c r="CK72" s="3"/>
-      <c r="CL72" s="3"/>
-      <c r="CM72" s="3"/>
-    </row>
-    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="73" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="4" t="s">
         <v>153</v>
       </c>
       <c r="U73" s="3"/>
@@ -4663,47 +4653,6 @@
       <c r="AT73" s="3"/>
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
-      <c r="AY73" s="3"/>
-      <c r="AZ73" s="3"/>
-      <c r="BA73" s="3"/>
-      <c r="BB73" s="3"/>
-      <c r="BC73" s="3"/>
-      <c r="BD73" s="3"/>
-      <c r="BE73" s="3"/>
-      <c r="BF73" s="3"/>
-      <c r="BG73" s="3"/>
-      <c r="BH73" s="3"/>
-      <c r="BI73" s="3"/>
-      <c r="BJ73" s="3"/>
-      <c r="BK73" s="3"/>
-      <c r="BL73" s="3"/>
-      <c r="BM73" s="3"/>
-      <c r="BN73" s="3"/>
-      <c r="BO73" s="3"/>
-      <c r="BP73" s="3"/>
-      <c r="BQ73" s="3"/>
-      <c r="BR73" s="3"/>
-      <c r="BS73" s="3"/>
-      <c r="BT73" s="3"/>
-      <c r="BU73" s="3"/>
-      <c r="BV73" s="3"/>
-      <c r="BW73" s="3"/>
-      <c r="BX73" s="3"/>
-      <c r="BY73" s="3"/>
-      <c r="BZ73" s="3"/>
-      <c r="CA73" s="3"/>
-      <c r="CB73" s="3"/>
-      <c r="CC73" s="3"/>
-      <c r="CD73" s="3"/>
-      <c r="CE73" s="3"/>
-      <c r="CF73" s="3"/>
-      <c r="CG73" s="3"/>
-      <c r="CH73" s="3"/>
-      <c r="CI73" s="3"/>
-      <c r="CJ73" s="3"/>
-      <c r="CK73" s="3"/>
-      <c r="CL73" s="3"/>
-      <c r="CM73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
@@ -4782,11 +4731,11 @@
       <c r="CL74" s="3"/>
       <c r="CM74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="5" t="s">
+      <c r="B75" s="1" t="s">
         <v>157</v>
       </c>
       <c r="U75" s="3"/>
@@ -4859,11 +4808,11 @@
       <c r="CL75" s="3"/>
       <c r="CM75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="1" t="s">
         <v>159</v>
       </c>
       <c r="U76" s="3"/>
@@ -4936,11 +4885,11 @@
       <c r="CL76" s="3"/>
       <c r="CM76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="4" t="s">
         <v>161</v>
       </c>
       <c r="U77" s="3"/>
@@ -5013,11 +4962,11 @@
       <c r="CL77" s="3"/>
       <c r="CM77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="4" t="s">
         <v>163</v>
       </c>
       <c r="U78" s="3"/>
@@ -5090,11 +5039,11 @@
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="4" t="s">
         <v>165</v>
       </c>
       <c r="U79" s="3"/>
@@ -5167,11 +5116,11 @@
       <c r="CL79" s="3"/>
       <c r="CM79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="4" t="s">
         <v>167</v>
       </c>
       <c r="U80" s="3"/>
@@ -5244,11 +5193,11 @@
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="5" t="s">
+      <c r="B81" s="4" t="s">
         <v>169</v>
       </c>
       <c r="U81" s="3"/>
@@ -5326,7 +5275,7 @@
         <v>170</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>132</v>
+        <v>171</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
@@ -5398,12 +5347,12 @@
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>132</v>
+        <v>172</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>173</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
@@ -5477,10 +5426,10 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
@@ -5554,10 +5503,10 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
@@ -5631,10 +5580,10 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
@@ -5708,10 +5657,10 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
@@ -5783,12 +5732,12 @@
       <c r="CL87" s="3"/>
       <c r="CM87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="B88" s="5" t="s">
-        <v>177</v>
+        <v>178</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
@@ -5862,10 +5811,10 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>179</v>
+        <v>136</v>
       </c>
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
@@ -5937,11 +5886,11 @@
       <c r="CL89" s="3"/>
       <c r="CM89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="4" t="s">
         <v>181</v>
       </c>
       <c r="U90" s="3"/>
@@ -6021,6 +5970,34 @@
       <c r="B91" s="1" t="s">
         <v>183</v>
       </c>
+      <c r="U91" s="3"/>
+      <c r="V91" s="3"/>
+      <c r="W91" s="3"/>
+      <c r="X91" s="3"/>
+      <c r="Y91" s="3"/>
+      <c r="Z91" s="3"/>
+      <c r="AA91" s="3"/>
+      <c r="AB91" s="3"/>
+      <c r="AC91" s="3"/>
+      <c r="AD91" s="3"/>
+      <c r="AE91" s="3"/>
+      <c r="AF91" s="3"/>
+      <c r="AG91" s="3"/>
+      <c r="AH91" s="3"/>
+      <c r="AI91" s="3"/>
+      <c r="AJ91" s="3"/>
+      <c r="AK91" s="3"/>
+      <c r="AL91" s="3"/>
+      <c r="AM91" s="3"/>
+      <c r="AN91" s="3"/>
+      <c r="AO91" s="3"/>
+      <c r="AP91" s="3"/>
+      <c r="AQ91" s="3"/>
+      <c r="AR91" s="3"/>
+      <c r="AS91" s="3"/>
+      <c r="AT91" s="3"/>
+      <c r="AU91" s="3"/>
+      <c r="AV91" s="3"/>
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
       <c r="BA91" s="3"/>
@@ -6063,13 +6040,41 @@
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="1" t="s">
-        <v>132</v>
-      </c>
+      <c r="B92" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="U92" s="3"/>
+      <c r="V92" s="3"/>
+      <c r="W92" s="3"/>
+      <c r="X92" s="3"/>
+      <c r="Y92" s="3"/>
+      <c r="Z92" s="3"/>
+      <c r="AA92" s="3"/>
+      <c r="AB92" s="3"/>
+      <c r="AC92" s="3"/>
+      <c r="AD92" s="3"/>
+      <c r="AE92" s="3"/>
+      <c r="AF92" s="3"/>
+      <c r="AG92" s="3"/>
+      <c r="AH92" s="3"/>
+      <c r="AI92" s="3"/>
+      <c r="AJ92" s="3"/>
+      <c r="AK92" s="3"/>
+      <c r="AL92" s="3"/>
+      <c r="AM92" s="3"/>
+      <c r="AN92" s="3"/>
+      <c r="AO92" s="3"/>
+      <c r="AP92" s="3"/>
+      <c r="AQ92" s="3"/>
+      <c r="AR92" s="3"/>
+      <c r="AS92" s="3"/>
+      <c r="AT92" s="3"/>
+      <c r="AU92" s="3"/>
+      <c r="AV92" s="3"/>
       <c r="AY92" s="3"/>
       <c r="AZ92" s="3"/>
       <c r="BA92" s="3"/>
@@ -6113,8 +6118,11 @@
       <c r="CM92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="5" t="s">
-        <v>185</v>
+      <c r="A93" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="AY93" s="3"/>
       <c r="AZ93" s="3"/>
@@ -6158,12 +6166,12 @@
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B94" s="5" t="s">
-        <v>187</v>
+        <v>188</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>136</v>
       </c>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
@@ -6208,11 +6216,8 @@
       <c r="CM94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B95" s="1" t="s">
-        <v>132</v>
+      <c r="A95" s="4" t="s">
+        <v>189</v>
       </c>
       <c r="AY95" s="3"/>
       <c r="AZ95" s="3"/>
@@ -6256,12 +6261,12 @@
       <c r="CL95" s="3"/>
       <c r="CM95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="B96" s="5" t="s">
         <v>190</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="AY96" s="3"/>
       <c r="AZ96" s="3"/>
@@ -6305,31 +6310,13 @@
       <c r="CL96" s="3"/>
       <c r="CM96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="8" t="s">
-        <v>191</v>
-      </c>
-      <c r="B97" s="5" t="s">
+    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="C97" s="8"/>
-      <c r="D97" s="8"/>
-      <c r="E97" s="8"/>
-      <c r="F97" s="8"/>
-      <c r="G97" s="8"/>
-      <c r="H97" s="8"/>
-      <c r="I97" s="8"/>
-      <c r="J97" s="8"/>
-      <c r="K97" s="8"/>
-      <c r="L97" s="8"/>
-      <c r="M97" s="8"/>
-      <c r="N97" s="8"/>
-      <c r="O97" s="8"/>
-      <c r="P97" s="8"/>
-      <c r="Q97" s="8"/>
-      <c r="R97" s="8"/>
-      <c r="S97" s="8"/>
-      <c r="T97" s="8"/>
+      <c r="B97" s="1" t="s">
+        <v>136</v>
+      </c>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
       <c r="BA97" s="3"/>
@@ -6372,11 +6359,11 @@
       <c r="CL97" s="3"/>
       <c r="CM97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>194</v>
       </c>
       <c r="AY98" s="3"/>
@@ -6421,13 +6408,31 @@
       <c r="CL98" s="3"/>
       <c r="CM98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="1" t="s">
+    <row r="99" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="8" t="s">
         <v>195</v>
       </c>
-      <c r="B99" s="5" t="s">
+      <c r="B99" s="4" t="s">
         <v>196</v>
       </c>
+      <c r="C99" s="8"/>
+      <c r="D99" s="8"/>
+      <c r="E99" s="8"/>
+      <c r="F99" s="8"/>
+      <c r="G99" s="8"/>
+      <c r="H99" s="8"/>
+      <c r="I99" s="8"/>
+      <c r="J99" s="8"/>
+      <c r="K99" s="8"/>
+      <c r="L99" s="8"/>
+      <c r="M99" s="8"/>
+      <c r="N99" s="8"/>
+      <c r="O99" s="8"/>
+      <c r="P99" s="8"/>
+      <c r="Q99" s="8"/>
+      <c r="R99" s="8"/>
+      <c r="S99" s="8"/>
+      <c r="T99" s="8"/>
       <c r="AY99" s="3"/>
       <c r="AZ99" s="3"/>
       <c r="BA99" s="3"/>
@@ -6470,67 +6475,60 @@
       <c r="CL99" s="3"/>
       <c r="CM99" s="3"/>
     </row>
-    <row r="100" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B100" s="5" t="s">
+      <c r="B100" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="C100" s="1"/>
-      <c r="D100" s="1"/>
-      <c r="E100" s="1"/>
-      <c r="F100" s="1"/>
-      <c r="G100" s="1"/>
-      <c r="H100" s="1"/>
-      <c r="I100" s="1"/>
-      <c r="J100" s="1"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="1"/>
-      <c r="M100" s="1"/>
-      <c r="N100" s="1"/>
-      <c r="O100" s="1"/>
-      <c r="P100" s="1"/>
-      <c r="Q100" s="1"/>
-      <c r="R100" s="1"/>
-      <c r="S100" s="1"/>
-      <c r="T100" s="1"/>
-      <c r="U100" s="1"/>
-      <c r="V100" s="1"/>
-      <c r="W100" s="1"/>
-      <c r="X100" s="1"/>
-      <c r="Y100" s="1"/>
-      <c r="Z100" s="1"/>
-      <c r="AA100" s="1"/>
-      <c r="AB100" s="1"/>
-      <c r="AC100" s="1"/>
-      <c r="AD100" s="1"/>
-      <c r="AE100" s="1"/>
-      <c r="AF100" s="1"/>
-      <c r="AG100" s="1"/>
-      <c r="AH100" s="1"/>
-      <c r="AI100" s="1"/>
-      <c r="AJ100" s="1"/>
-      <c r="AK100" s="1"/>
-      <c r="AL100" s="1"/>
-      <c r="AM100" s="1"/>
-      <c r="AN100" s="1"/>
-      <c r="AO100" s="1"/>
-      <c r="AP100" s="1"/>
-      <c r="AQ100" s="1"/>
-      <c r="AR100" s="1"/>
-      <c r="AS100" s="1"/>
-      <c r="AT100" s="1"/>
-      <c r="AU100" s="1"/>
-      <c r="AV100" s="1"/>
-      <c r="AW100" s="1"/>
-      <c r="AX100" s="1"/>
-    </row>
-    <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY100" s="3"/>
+      <c r="AZ100" s="3"/>
+      <c r="BA100" s="3"/>
+      <c r="BB100" s="3"/>
+      <c r="BC100" s="3"/>
+      <c r="BD100" s="3"/>
+      <c r="BE100" s="3"/>
+      <c r="BF100" s="3"/>
+      <c r="BG100" s="3"/>
+      <c r="BH100" s="3"/>
+      <c r="BI100" s="3"/>
+      <c r="BJ100" s="3"/>
+      <c r="BK100" s="3"/>
+      <c r="BL100" s="3"/>
+      <c r="BM100" s="3"/>
+      <c r="BN100" s="3"/>
+      <c r="BO100" s="3"/>
+      <c r="BP100" s="3"/>
+      <c r="BQ100" s="3"/>
+      <c r="BR100" s="3"/>
+      <c r="BS100" s="3"/>
+      <c r="BT100" s="3"/>
+      <c r="BU100" s="3"/>
+      <c r="BV100" s="3"/>
+      <c r="BW100" s="3"/>
+      <c r="BX100" s="3"/>
+      <c r="BY100" s="3"/>
+      <c r="BZ100" s="3"/>
+      <c r="CA100" s="3"/>
+      <c r="CB100" s="3"/>
+      <c r="CC100" s="3"/>
+      <c r="CD100" s="3"/>
+      <c r="CE100" s="3"/>
+      <c r="CF100" s="3"/>
+      <c r="CG100" s="3"/>
+      <c r="CH100" s="3"/>
+      <c r="CI100" s="3"/>
+      <c r="CJ100" s="3"/>
+      <c r="CK100" s="3"/>
+      <c r="CL100" s="3"/>
+      <c r="CM100" s="3"/>
+    </row>
+    <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="5" t="s">
+      <c r="B101" s="4" t="s">
         <v>200</v>
       </c>
       <c r="AY101" s="3"/>
@@ -6575,521 +6573,626 @@
       <c r="CL101" s="3"/>
       <c r="CM101" s="3"/>
     </row>
-    <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="5" t="s">
+      <c r="B102" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="AY102" s="3"/>
-      <c r="AZ102" s="3"/>
-      <c r="BA102" s="3"/>
-      <c r="BB102" s="3"/>
-      <c r="BC102" s="3"/>
-      <c r="BD102" s="3"/>
-      <c r="BE102" s="3"/>
-      <c r="BF102" s="3"/>
-      <c r="BG102" s="3"/>
-      <c r="BH102" s="3"/>
-      <c r="BI102" s="3"/>
-      <c r="BJ102" s="3"/>
-      <c r="BK102" s="3"/>
-      <c r="BL102" s="3"/>
-      <c r="BM102" s="3"/>
-      <c r="BN102" s="3"/>
-      <c r="BO102" s="3"/>
-      <c r="BP102" s="3"/>
-      <c r="BQ102" s="3"/>
-      <c r="BR102" s="3"/>
-      <c r="BS102" s="3"/>
-      <c r="BT102" s="3"/>
-      <c r="BU102" s="3"/>
-      <c r="BV102" s="3"/>
-      <c r="BW102" s="3"/>
-      <c r="BX102" s="3"/>
-      <c r="BY102" s="3"/>
-      <c r="BZ102" s="3"/>
-      <c r="CA102" s="3"/>
-      <c r="CB102" s="3"/>
-      <c r="CC102" s="3"/>
-      <c r="CD102" s="3"/>
-      <c r="CE102" s="3"/>
-      <c r="CF102" s="3"/>
-      <c r="CG102" s="3"/>
-      <c r="CH102" s="3"/>
-      <c r="CI102" s="3"/>
-      <c r="CJ102" s="3"/>
-      <c r="CK102" s="3"/>
-      <c r="CL102" s="3"/>
-      <c r="CM102" s="3"/>
-    </row>
-    <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C102" s="1"/>
+      <c r="D102" s="1"/>
+      <c r="E102" s="1"/>
+      <c r="F102" s="1"/>
+      <c r="G102" s="1"/>
+      <c r="H102" s="1"/>
+      <c r="I102" s="1"/>
+      <c r="J102" s="1"/>
+      <c r="K102" s="1"/>
+      <c r="L102" s="1"/>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1"/>
+      <c r="V102" s="1"/>
+      <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
+      <c r="Z102" s="1"/>
+      <c r="AA102" s="1"/>
+      <c r="AB102" s="1"/>
+      <c r="AC102" s="1"/>
+      <c r="AD102" s="1"/>
+      <c r="AE102" s="1"/>
+      <c r="AF102" s="1"/>
+      <c r="AG102" s="1"/>
+      <c r="AH102" s="1"/>
+      <c r="AI102" s="1"/>
+      <c r="AJ102" s="1"/>
+      <c r="AK102" s="1"/>
+      <c r="AL102" s="1"/>
+      <c r="AM102" s="1"/>
+      <c r="AN102" s="1"/>
+      <c r="AO102" s="1"/>
+      <c r="AP102" s="1"/>
+      <c r="AQ102" s="1"/>
+      <c r="AR102" s="1"/>
+      <c r="AS102" s="1"/>
+      <c r="AT102" s="1"/>
+      <c r="AU102" s="1"/>
+      <c r="AV102" s="1"/>
+      <c r="AW102" s="1"/>
+      <c r="AX102" s="1"/>
+    </row>
+    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B103" s="5" t="s">
+      <c r="B103" s="4" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY103" s="3"/>
+      <c r="AZ103" s="3"/>
+      <c r="BA103" s="3"/>
+      <c r="BB103" s="3"/>
+      <c r="BC103" s="3"/>
+      <c r="BD103" s="3"/>
+      <c r="BE103" s="3"/>
+      <c r="BF103" s="3"/>
+      <c r="BG103" s="3"/>
+      <c r="BH103" s="3"/>
+      <c r="BI103" s="3"/>
+      <c r="BJ103" s="3"/>
+      <c r="BK103" s="3"/>
+      <c r="BL103" s="3"/>
+      <c r="BM103" s="3"/>
+      <c r="BN103" s="3"/>
+      <c r="BO103" s="3"/>
+      <c r="BP103" s="3"/>
+      <c r="BQ103" s="3"/>
+      <c r="BR103" s="3"/>
+      <c r="BS103" s="3"/>
+      <c r="BT103" s="3"/>
+      <c r="BU103" s="3"/>
+      <c r="BV103" s="3"/>
+      <c r="BW103" s="3"/>
+      <c r="BX103" s="3"/>
+      <c r="BY103" s="3"/>
+      <c r="BZ103" s="3"/>
+      <c r="CA103" s="3"/>
+      <c r="CB103" s="3"/>
+      <c r="CC103" s="3"/>
+      <c r="CD103" s="3"/>
+      <c r="CE103" s="3"/>
+      <c r="CF103" s="3"/>
+      <c r="CG103" s="3"/>
+      <c r="CH103" s="3"/>
+      <c r="CI103" s="3"/>
+      <c r="CJ103" s="3"/>
+      <c r="CK103" s="3"/>
+      <c r="CL103" s="3"/>
+      <c r="CM103" s="3"/>
+    </row>
+    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B104" s="5" t="s">
+      <c r="B104" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="C104" s="5"/>
-      <c r="D104" s="5"/>
-      <c r="E104" s="5"/>
-      <c r="F104" s="5"/>
-      <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
-      <c r="J104" s="5"/>
-      <c r="K104" s="5"/>
-      <c r="L104" s="5"/>
-      <c r="M104" s="5"/>
-      <c r="N104" s="5"/>
-      <c r="O104" s="5"/>
-      <c r="P104" s="5"/>
-      <c r="Q104" s="5"/>
-      <c r="R104" s="5"/>
-      <c r="S104" s="5"/>
-      <c r="T104" s="5"/>
-    </row>
-    <row r="105" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="4" t="s">
+      <c r="AY104" s="3"/>
+      <c r="AZ104" s="3"/>
+      <c r="BA104" s="3"/>
+      <c r="BB104" s="3"/>
+      <c r="BC104" s="3"/>
+      <c r="BD104" s="3"/>
+      <c r="BE104" s="3"/>
+      <c r="BF104" s="3"/>
+      <c r="BG104" s="3"/>
+      <c r="BH104" s="3"/>
+      <c r="BI104" s="3"/>
+      <c r="BJ104" s="3"/>
+      <c r="BK104" s="3"/>
+      <c r="BL104" s="3"/>
+      <c r="BM104" s="3"/>
+      <c r="BN104" s="3"/>
+      <c r="BO104" s="3"/>
+      <c r="BP104" s="3"/>
+      <c r="BQ104" s="3"/>
+      <c r="BR104" s="3"/>
+      <c r="BS104" s="3"/>
+      <c r="BT104" s="3"/>
+      <c r="BU104" s="3"/>
+      <c r="BV104" s="3"/>
+      <c r="BW104" s="3"/>
+      <c r="BX104" s="3"/>
+      <c r="BY104" s="3"/>
+      <c r="BZ104" s="3"/>
+      <c r="CA104" s="3"/>
+      <c r="CB104" s="3"/>
+      <c r="CC104" s="3"/>
+      <c r="CD104" s="3"/>
+      <c r="CE104" s="3"/>
+      <c r="CF104" s="3"/>
+      <c r="CG104" s="3"/>
+      <c r="CH104" s="3"/>
+      <c r="CI104" s="3"/>
+      <c r="CJ104" s="3"/>
+      <c r="CK104" s="3"/>
+      <c r="CL104" s="3"/>
+      <c r="CM104" s="3"/>
+    </row>
+    <row r="105" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
-      <c r="K105" s="5"/>
-      <c r="L105" s="5"/>
-      <c r="M105" s="5"/>
-      <c r="N105" s="5"/>
-      <c r="O105" s="5"/>
-      <c r="P105" s="5"/>
-      <c r="Q105" s="5"/>
-      <c r="R105" s="5"/>
-      <c r="S105" s="5"/>
-      <c r="T105" s="5"/>
-    </row>
-    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B106" s="5" t="s">
+      <c r="B106" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="5"/>
-      <c r="D106" s="5"/>
-      <c r="E106" s="5"/>
-      <c r="F106" s="5"/>
-      <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
-      <c r="I106" s="5"/>
-      <c r="J106" s="5"/>
-      <c r="K106" s="5"/>
-      <c r="L106" s="5"/>
-      <c r="M106" s="5"/>
-      <c r="N106" s="5"/>
-      <c r="O106" s="5"/>
-      <c r="P106" s="5"/>
-      <c r="Q106" s="5"/>
-      <c r="R106" s="5"/>
-      <c r="S106" s="5"/>
-      <c r="T106" s="5"/>
-    </row>
-    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="1" t="s">
+      <c r="C106" s="4"/>
+      <c r="D106" s="4"/>
+      <c r="E106" s="4"/>
+      <c r="F106" s="4"/>
+      <c r="G106" s="4"/>
+      <c r="H106" s="4"/>
+      <c r="I106" s="4"/>
+      <c r="J106" s="4"/>
+      <c r="K106" s="4"/>
+      <c r="L106" s="4"/>
+      <c r="M106" s="4"/>
+      <c r="N106" s="4"/>
+      <c r="O106" s="4"/>
+      <c r="P106" s="4"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="4"/>
+      <c r="T106" s="4"/>
+    </row>
+    <row r="107" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="5" t="s">
         <v>211</v>
       </c>
-      <c r="B107" s="1" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="108" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="C107" s="4"/>
+      <c r="D107" s="4"/>
+      <c r="E107" s="4"/>
+      <c r="F107" s="4"/>
+      <c r="G107" s="4"/>
+      <c r="H107" s="4"/>
+      <c r="I107" s="4"/>
+      <c r="J107" s="4"/>
+      <c r="K107" s="4"/>
+      <c r="L107" s="4"/>
+      <c r="M107" s="4"/>
+      <c r="N107" s="4"/>
+      <c r="O107" s="4"/>
+      <c r="P107" s="4"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="4"/>
+      <c r="T107" s="4"/>
+    </row>
+    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="B108" s="5" t="s">
         <v>213</v>
       </c>
-    </row>
-    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C108" s="4"/>
+      <c r="D108" s="4"/>
+      <c r="E108" s="4"/>
+      <c r="F108" s="4"/>
+      <c r="G108" s="4"/>
+      <c r="H108" s="4"/>
+      <c r="I108" s="4"/>
+      <c r="J108" s="4"/>
+      <c r="K108" s="4"/>
+      <c r="L108" s="4"/>
+      <c r="M108" s="4"/>
+      <c r="N108" s="4"/>
+      <c r="O108" s="4"/>
+      <c r="P108" s="4"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="4"/>
+      <c r="T108" s="4"/>
+    </row>
+    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="B109" s="5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B110" s="5" t="s">
+      <c r="B110" s="4" t="s">
         <v>217</v>
       </c>
-      <c r="C110" s="5"/>
-      <c r="D110" s="5"/>
-      <c r="E110" s="5"/>
-      <c r="F110" s="5"/>
-      <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
-      <c r="J110" s="5"/>
-      <c r="K110" s="5"/>
-      <c r="L110" s="5"/>
-      <c r="M110" s="5"/>
-      <c r="N110" s="5"/>
-      <c r="O110" s="5"/>
-      <c r="P110" s="5"/>
-      <c r="Q110" s="5"/>
-      <c r="R110" s="5"/>
-      <c r="S110" s="5"/>
-      <c r="T110" s="5"/>
-    </row>
-    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B111" s="5" t="s">
+      <c r="B111" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="C111" s="5"/>
-      <c r="D111" s="5"/>
-      <c r="E111" s="5"/>
-      <c r="F111" s="5"/>
-      <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
-      <c r="J111" s="5"/>
-      <c r="K111" s="5"/>
-      <c r="L111" s="5"/>
-      <c r="M111" s="5"/>
-      <c r="N111" s="5"/>
-      <c r="O111" s="5"/>
-      <c r="P111" s="5"/>
-      <c r="Q111" s="5"/>
-      <c r="R111" s="5"/>
-      <c r="S111" s="5"/>
-      <c r="T111" s="5"/>
-    </row>
-    <row r="112" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="112" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="5" t="s">
+      <c r="C112" s="4"/>
+      <c r="D112" s="4"/>
+      <c r="E112" s="4"/>
+      <c r="F112" s="4"/>
+      <c r="G112" s="4"/>
+      <c r="H112" s="4"/>
+      <c r="I112" s="4"/>
+      <c r="J112" s="4"/>
+      <c r="K112" s="4"/>
+      <c r="L112" s="4"/>
+      <c r="M112" s="4"/>
+      <c r="N112" s="4"/>
+      <c r="O112" s="4"/>
+      <c r="P112" s="4"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="4"/>
+      <c r="T112" s="4"/>
+    </row>
+    <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="1" t="s">
         <v>222</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="B113" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="E112" s="5" t="s">
+      <c r="C113" s="4"/>
+      <c r="D113" s="4"/>
+      <c r="E113" s="4"/>
+      <c r="F113" s="4"/>
+      <c r="G113" s="4"/>
+      <c r="H113" s="4"/>
+      <c r="I113" s="4"/>
+      <c r="J113" s="4"/>
+      <c r="K113" s="4"/>
+      <c r="L113" s="4"/>
+      <c r="M113" s="4"/>
+      <c r="N113" s="4"/>
+      <c r="O113" s="4"/>
+      <c r="P113" s="4"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="4"/>
+      <c r="T113" s="4"/>
+    </row>
+    <row r="114" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="F112" s="5" t="s">
+      <c r="B114" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="C114" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="H112" s="5" t="s">
+      <c r="D114" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="I112" s="5" t="s">
+      <c r="E114" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="J112" s="5" t="s">
+      <c r="F114" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="K112" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="L112" s="5" t="s">
+      <c r="H114" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="M112" s="5" t="s">
+      <c r="I114" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="N112" s="5" t="s">
+      <c r="J114" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="O112" s="5" t="s">
+      <c r="K114" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="P112" s="5" t="s">
+      <c r="L114" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="Q112" s="5" t="s">
+      <c r="M114" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="R112" s="5" t="s">
+      <c r="N114" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="S112" s="5" t="s">
+      <c r="O114" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="T112" s="5" t="s">
+      <c r="P114" s="4" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="113" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A113" s="1" t="s">
+      <c r="Q114" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B113" s="5" t="s">
+      <c r="R114" s="4" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="114" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A114" s="1" t="s">
+      <c r="S114" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B114" s="5" t="s">
+      <c r="T114" s="4" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="8" t="s">
+    <row r="115" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B115" s="5" t="s">
+      <c r="B115" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="C115" s="8"/>
-      <c r="D115" s="8"/>
-      <c r="E115" s="8"/>
-      <c r="F115" s="8"/>
-      <c r="G115" s="8"/>
-      <c r="H115" s="8"/>
-      <c r="I115" s="8"/>
-      <c r="J115" s="8"/>
-      <c r="K115" s="8"/>
-      <c r="L115" s="8"/>
-      <c r="M115" s="8"/>
-      <c r="N115" s="8"/>
-      <c r="O115" s="8"/>
-      <c r="P115" s="8"/>
-      <c r="Q115" s="8"/>
-      <c r="R115" s="8"/>
-      <c r="S115" s="8"/>
-      <c r="T115" s="8"/>
-    </row>
-    <row r="116" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="116" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B116" s="9" t="s">
+      <c r="B116" s="4" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="1" t="s">
+    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="B117" s="9" t="s">
+      <c r="B117" s="4" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="118" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C117" s="8"/>
+      <c r="D117" s="8"/>
+      <c r="E117" s="8"/>
+      <c r="F117" s="8"/>
+      <c r="G117" s="8"/>
+      <c r="H117" s="8"/>
+      <c r="I117" s="8"/>
+      <c r="J117" s="8"/>
+      <c r="K117" s="8"/>
+      <c r="L117" s="8"/>
+      <c r="M117" s="8"/>
+      <c r="N117" s="8"/>
+      <c r="O117" s="8"/>
+      <c r="P117" s="8"/>
+      <c r="Q117" s="8"/>
+      <c r="R117" s="8"/>
+      <c r="S117" s="8"/>
+      <c r="T117" s="8"/>
+    </row>
+    <row r="118" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B118" s="5" t="s">
+      <c r="B118" s="9" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="1" t="s">
+      <c r="B119" s="9" t="s">
         <v>253</v>
       </c>
-      <c r="C119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="D119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="E119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="F119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="G119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="H119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="I119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="K119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="L119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="M119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="N119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="O119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="P119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="Q119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="R119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="S119" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="T119" s="1" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="120" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="120" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="4" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B121" s="5" t="s">
+      <c r="B121" s="1" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="E121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="F121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="G121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="H121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="I121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="J121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="K121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="L121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="M121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="N121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="O121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="P121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="R121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="S121" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="T121" s="1" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B122" s="1" t="s">
+      <c r="B122" s="4" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B123" s="1" t="s">
+      <c r="B123" s="4" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B124" s="5" t="s">
+      <c r="B124" s="1" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B125" s="5" t="s">
+      <c r="B125" s="1" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B126" s="5" t="s">
+      <c r="B126" s="4" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B127" s="5" t="s">
+      <c r="B127" s="4" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B128" s="5" t="s">
+      <c r="B128" s="4" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B129" s="5" t="s">
+      <c r="B129" s="4" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B130" s="5" t="s">
+      <c r="B130" s="4" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B131" s="9" t="s">
+      <c r="B131" s="4" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B132" s="9" t="s">
+      <c r="B132" s="4" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B133" s="5" t="s">
+      <c r="B133" s="9" t="s">
         <v>281</v>
       </c>
     </row>
+    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="135" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="1" t="s">
+        <v>284</v>
+      </c>
+      <c r="B135" s="4" t="s">
+        <v>285</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A2:T132"/>
+  <autoFilter ref="A2:T134"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/new original/EN/Data/chara_talk.xlsx
+++ b/new original/EN/Data/chara_talk.xlsx
@@ -11,7 +11,7 @@
     <sheet name="1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$134</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'1'!$A$2:$T$132</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="286">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="282">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -83,37 +83,6 @@
   </si>
   <si>
     <t xml:space="preserve">hope</t>
-  </si>
-  <si>
-    <t xml:space="preserve">play_baby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mommy!
-Mama!
-Baba!
-Baba baba!
-Waaah!
-Where’s Mommy?
-Are you Mommy?
-…Mommy?
-…Mommy! </t>
-  </si>
-  <si>
-    <t xml:space="preserve">play_mama</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There, there.
-Mommy’s here~
-Good boy, good boy.
-There, there.
-Mommy’s here.
-Mm-hmm, mm-hmm.
-It’s okay, it’s okay.
-Big hug!
-Hug.
-Mommy’s right here.
-Go on, you can be needy.
-I’ll take it all in.</t>
   </si>
   <si>
     <t xml:space="preserve">kiss</t>
@@ -1605,12 +1574,12 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1669,9 +1638,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>2376000</xdr:colOff>
+      <xdr:colOff>2376360</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>124200</xdr:rowOff>
+      <xdr:rowOff>124560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1681,7 +1650,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="50980680" cy="124200"/>
+          <a:ext cx="50981040" cy="124560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1714,9 +1683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>18</xdr:col>
-      <xdr:colOff>515520</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
+      <xdr:colOff>515880</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>63000</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1726,7 +1695,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="0"/>
-          <a:ext cx="55508400" cy="49148280"/>
+          <a:ext cx="55508760" cy="46324800"/>
         </a:xfrm>
         <a:solidFill>
           <a:srgbClr val="ffffff"/>
@@ -1861,7 +1830,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:CM135"/>
+  <dimension ref="A1:CM133"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.04"/>
@@ -2038,7 +2007,7 @@
       <c r="AU3" s="3"/>
       <c r="AV3" s="3"/>
     </row>
-    <row r="4" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>20</v>
       </c>
@@ -2074,11 +2043,11 @@
       <c r="AU4" s="3"/>
       <c r="AV4" s="3"/>
     </row>
-    <row r="5" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>23</v>
       </c>
       <c r="U5" s="3"/>
@@ -2110,7 +2079,7 @@
       <c r="AU5" s="3"/>
       <c r="AV5" s="3"/>
     </row>
-    <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2146,11 +2115,11 @@
       <c r="AU6" s="3"/>
       <c r="AV6" s="3"/>
     </row>
-    <row r="7" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="U7" s="3"/>
@@ -2182,11 +2151,11 @@
       <c r="AU7" s="3"/>
       <c r="AV7" s="3"/>
     </row>
-    <row r="8" customFormat="false" ht="220.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="1" t="s">
         <v>29</v>
       </c>
       <c r="U8" s="3"/>
@@ -2222,7 +2191,7 @@
       <c r="A9" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="6" t="s">
         <v>31</v>
       </c>
       <c r="U9" s="3"/>
@@ -2254,11 +2223,11 @@
       <c r="AU9" s="3"/>
       <c r="AV9" s="3"/>
     </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="5" t="s">
         <v>33</v>
       </c>
       <c r="U10" s="3"/>
@@ -2290,11 +2259,11 @@
       <c r="AU10" s="3"/>
       <c r="AV10" s="3"/>
     </row>
-    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>35</v>
       </c>
       <c r="U11" s="3"/>
@@ -2326,83 +2295,65 @@
       <c r="AU11" s="3"/>
       <c r="AV11" s="3"/>
     </row>
-    <row r="12" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="U12" s="3"/>
-      <c r="V12" s="3"/>
-      <c r="W12" s="3"/>
-      <c r="X12" s="3"/>
-      <c r="Y12" s="3"/>
-      <c r="Z12" s="3"/>
-      <c r="AA12" s="3"/>
-      <c r="AB12" s="3"/>
-      <c r="AC12" s="3"/>
-      <c r="AD12" s="3"/>
-      <c r="AE12" s="3"/>
-      <c r="AF12" s="3"/>
-      <c r="AG12" s="3"/>
-      <c r="AH12" s="3"/>
-      <c r="AI12" s="3"/>
-      <c r="AJ12" s="3"/>
-      <c r="AK12" s="3"/>
-      <c r="AL12" s="3"/>
-      <c r="AM12" s="3"/>
-      <c r="AN12" s="3"/>
-      <c r="AO12" s="3"/>
-      <c r="AP12" s="3"/>
-      <c r="AQ12" s="3"/>
-      <c r="AR12" s="3"/>
-      <c r="AS12" s="3"/>
-      <c r="AT12" s="3"/>
-      <c r="AU12" s="3"/>
-      <c r="AV12" s="3"/>
-    </row>
-    <row r="13" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
+      <c r="N12" s="1"/>
+      <c r="O12" s="1"/>
+      <c r="P12" s="1"/>
+      <c r="Q12" s="1"/>
+      <c r="R12" s="1"/>
+      <c r="S12" s="1"/>
+      <c r="T12" s="1"/>
+      <c r="AW12" s="1"/>
+    </row>
+    <row r="13" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="U13" s="3"/>
-      <c r="V13" s="3"/>
-      <c r="W13" s="3"/>
-      <c r="X13" s="3"/>
-      <c r="Y13" s="3"/>
-      <c r="Z13" s="3"/>
-      <c r="AA13" s="3"/>
-      <c r="AB13" s="3"/>
-      <c r="AC13" s="3"/>
-      <c r="AD13" s="3"/>
-      <c r="AE13" s="3"/>
-      <c r="AF13" s="3"/>
-      <c r="AG13" s="3"/>
-      <c r="AH13" s="3"/>
-      <c r="AI13" s="3"/>
-      <c r="AJ13" s="3"/>
-      <c r="AK13" s="3"/>
-      <c r="AL13" s="3"/>
-      <c r="AM13" s="3"/>
-      <c r="AN13" s="3"/>
-      <c r="AO13" s="3"/>
-      <c r="AP13" s="3"/>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3"/>
-      <c r="AS13" s="3"/>
-      <c r="AT13" s="3"/>
-      <c r="AU13" s="3"/>
-      <c r="AV13" s="3"/>
-    </row>
-    <row r="14" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="P13" s="1"/>
+      <c r="Q13" s="1"/>
+      <c r="R13" s="1"/>
+      <c r="S13" s="1"/>
+      <c r="T13" s="1"/>
+      <c r="AW13" s="1"/>
+    </row>
+    <row r="14" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>41</v>
       </c>
       <c r="C14" s="1"/>
@@ -2425,11 +2376,11 @@
       <c r="T14" s="1"/>
       <c r="AW14" s="1"/>
     </row>
-    <row r="15" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="5" t="s">
         <v>43</v>
       </c>
       <c r="C15" s="1"/>
@@ -2452,11 +2403,11 @@
       <c r="T15" s="1"/>
       <c r="AW15" s="1"/>
     </row>
-    <row r="16" s="3" customFormat="true" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C16" s="1"/>
@@ -2479,11 +2430,11 @@
       <c r="T16" s="1"/>
       <c r="AW16" s="1"/>
     </row>
-    <row r="17" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="17" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="5" t="s">
         <v>47</v>
       </c>
       <c r="C17" s="1"/>
@@ -2506,67 +2457,87 @@
       <c r="T17" s="1"/>
       <c r="AW17" s="1"/>
     </row>
-    <row r="18" s="3" customFormat="true" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-      <c r="S18" s="1"/>
-      <c r="T18" s="1"/>
-      <c r="AW18" s="1"/>
-    </row>
-    <row r="19" s="3" customFormat="true" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="U18" s="3"/>
+      <c r="V18" s="3"/>
+      <c r="W18" s="3"/>
+      <c r="X18" s="3"/>
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="3"/>
+      <c r="AA18" s="3"/>
+      <c r="AB18" s="3"/>
+      <c r="AC18" s="3"/>
+      <c r="AD18" s="3"/>
+      <c r="AE18" s="3"/>
+      <c r="AF18" s="3"/>
+      <c r="AG18" s="3"/>
+      <c r="AH18" s="3"/>
+      <c r="AI18" s="3"/>
+      <c r="AJ18" s="3"/>
+      <c r="AK18" s="3"/>
+      <c r="AL18" s="3"/>
+      <c r="AM18" s="3"/>
+      <c r="AN18" s="3"/>
+      <c r="AO18" s="3"/>
+      <c r="AP18" s="3"/>
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3"/>
+      <c r="AT18" s="3"/>
+      <c r="AU18" s="3"/>
+      <c r="AV18" s="3"/>
+    </row>
+    <row r="19" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1"/>
-      <c r="AW19" s="1"/>
-    </row>
-    <row r="20" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="s">
+      <c r="C19" s="5"/>
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+      <c r="W19" s="3"/>
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="3"/>
+      <c r="AA19" s="3"/>
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+      <c r="AF19" s="3"/>
+      <c r="AG19" s="3"/>
+      <c r="AH19" s="3"/>
+      <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
+      <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
+      <c r="AT19" s="3"/>
+      <c r="AU19" s="3"/>
+      <c r="AV19" s="3"/>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>53</v>
       </c>
+      <c r="C20" s="5"/>
       <c r="U20" s="3"/>
       <c r="V20" s="3"/>
       <c r="W20" s="3"/>
@@ -2596,14 +2567,14 @@
       <c r="AU20" s="3"/>
       <c r="AV20" s="3"/>
     </row>
-    <row r="21" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="s">
+    <row r="21" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C21" s="4"/>
+      <c r="C21" s="5"/>
       <c r="U21" s="3"/>
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
@@ -2633,14 +2604,14 @@
       <c r="AU21" s="3"/>
       <c r="AV21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="4" t="s">
+    <row r="22" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C22" s="4"/>
+      <c r="C22" s="5"/>
       <c r="U22" s="3"/>
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
@@ -2670,14 +2641,14 @@
       <c r="AU22" s="3"/>
       <c r="AV22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="4" t="s">
+    <row r="23" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C23" s="4"/>
+      <c r="C23" s="5"/>
       <c r="U23" s="3"/>
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
@@ -2708,13 +2679,12 @@
       <c r="AV23" s="3"/>
     </row>
     <row r="24" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="4" t="s">
+      <c r="A24" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C24" s="4"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
@@ -2744,14 +2714,13 @@
       <c r="AU24" s="3"/>
       <c r="AV24" s="3"/>
     </row>
-    <row r="25" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C25" s="4"/>
       <c r="U25" s="3"/>
       <c r="V25" s="3"/>
       <c r="W25" s="3"/>
@@ -2781,13 +2750,14 @@
       <c r="AU25" s="3"/>
       <c r="AV25" s="3"/>
     </row>
-    <row r="26" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="26" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="7" t="s">
         <v>65</v>
       </c>
+      <c r="C26" s="7"/>
       <c r="U26" s="3"/>
       <c r="V26" s="3"/>
       <c r="W26" s="3"/>
@@ -2817,11 +2787,11 @@
       <c r="AU26" s="3"/>
       <c r="AV26" s="3"/>
     </row>
-    <row r="27" customFormat="false" ht="128.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B27" s="7" t="s">
+      <c r="B27" s="5" t="s">
         <v>67</v>
       </c>
       <c r="U27" s="3"/>
@@ -2853,14 +2823,14 @@
       <c r="AU27" s="3"/>
       <c r="AV27" s="3"/>
     </row>
-    <row r="28" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="B28" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="C28" s="7"/>
+      <c r="C28" s="5"/>
       <c r="U28" s="3"/>
       <c r="V28" s="3"/>
       <c r="W28" s="3"/>
@@ -2890,11 +2860,11 @@
       <c r="AU28" s="3"/>
       <c r="AV28" s="3"/>
     </row>
-    <row r="29" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="5" t="s">
         <v>71</v>
       </c>
       <c r="U29" s="3"/>
@@ -2926,14 +2896,13 @@
       <c r="AU29" s="3"/>
       <c r="AV29" s="3"/>
     </row>
-    <row r="30" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C30" s="4"/>
       <c r="U30" s="3"/>
       <c r="V30" s="3"/>
       <c r="W30" s="3"/>
@@ -2963,11 +2932,11 @@
       <c r="AU30" s="3"/>
       <c r="AV30" s="3"/>
     </row>
-    <row r="31" customFormat="false" ht="126.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="7" t="s">
         <v>75</v>
       </c>
       <c r="U31" s="3"/>
@@ -2999,11 +2968,11 @@
       <c r="AU31" s="3"/>
       <c r="AV31" s="3"/>
     </row>
-    <row r="32" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="5" t="s">
         <v>77</v>
       </c>
       <c r="U32" s="3"/>
@@ -3035,13 +3004,14 @@
       <c r="AU32" s="3"/>
       <c r="AV32" s="3"/>
     </row>
-    <row r="33" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="7" t="s">
+      <c r="B33" s="1" t="s">
         <v>79</v>
       </c>
+      <c r="C33" s="5"/>
       <c r="U33" s="3"/>
       <c r="V33" s="3"/>
       <c r="W33" s="3"/>
@@ -3071,11 +3041,11 @@
       <c r="AU33" s="3"/>
       <c r="AV33" s="3"/>
     </row>
-    <row r="34" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="5" t="s">
         <v>81</v>
       </c>
       <c r="U34" s="3"/>
@@ -3107,14 +3077,13 @@
       <c r="AU34" s="3"/>
       <c r="AV34" s="3"/>
     </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C35" s="4"/>
       <c r="U35" s="3"/>
       <c r="V35" s="3"/>
       <c r="W35" s="3"/>
@@ -3144,12 +3113,12 @@
       <c r="AU35" s="3"/>
       <c r="AV35" s="3"/>
     </row>
-    <row r="36" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="36" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>85</v>
+      <c r="B36" s="5" t="s">
+        <v>83</v>
       </c>
       <c r="U36" s="3"/>
       <c r="V36" s="3"/>
@@ -3180,12 +3149,12 @@
       <c r="AU36" s="3"/>
       <c r="AV36" s="3"/>
     </row>
-    <row r="37" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B37" s="5" t="s">
         <v>86</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="U37" s="3"/>
       <c r="V37" s="3"/>
@@ -3216,12 +3185,12 @@
       <c r="AU37" s="3"/>
       <c r="AV37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="199.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B38" s="5" t="s">
         <v>88</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>87</v>
       </c>
       <c r="U38" s="3"/>
       <c r="V38" s="3"/>
@@ -3252,11 +3221,11 @@
       <c r="AU38" s="3"/>
       <c r="AV38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="1" t="s">
         <v>90</v>
       </c>
       <c r="U39" s="3"/>
@@ -3288,11 +3257,11 @@
       <c r="AU39" s="3"/>
       <c r="AV39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="40" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="5" t="s">
         <v>92</v>
       </c>
       <c r="U40" s="3"/>
@@ -3324,11 +3293,11 @@
       <c r="AU40" s="3"/>
       <c r="AV40" s="3"/>
     </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="5" t="s">
         <v>94</v>
       </c>
       <c r="U41" s="3"/>
@@ -3360,11 +3329,11 @@
       <c r="AU41" s="3"/>
       <c r="AV41" s="3"/>
     </row>
-    <row r="42" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="42" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="5" t="s">
         <v>96</v>
       </c>
       <c r="U42" s="3"/>
@@ -3396,11 +3365,11 @@
       <c r="AU42" s="3"/>
       <c r="AV42" s="3"/>
     </row>
-    <row r="43" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="43" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="5" t="s">
         <v>98</v>
       </c>
       <c r="U43" s="3"/>
@@ -3436,7 +3405,7 @@
       <c r="A44" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="5" t="s">
         <v>100</v>
       </c>
       <c r="U44" s="3"/>
@@ -3468,11 +3437,11 @@
       <c r="AU44" s="3"/>
       <c r="AV44" s="3"/>
     </row>
-    <row r="45" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="5" t="s">
         <v>102</v>
       </c>
       <c r="U45" s="3"/>
@@ -3504,13 +3473,14 @@
       <c r="AU45" s="3"/>
       <c r="AV45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="5" t="s">
         <v>104</v>
       </c>
+      <c r="C46" s="5"/>
       <c r="U46" s="3"/>
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
@@ -3540,11 +3510,11 @@
       <c r="AU46" s="3"/>
       <c r="AV46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="1" t="s">
         <v>106</v>
       </c>
       <c r="U47" s="3"/>
@@ -3576,14 +3546,13 @@
       <c r="AU47" s="3"/>
       <c r="AV47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="48" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C48" s="4"/>
       <c r="U48" s="3"/>
       <c r="V48" s="3"/>
       <c r="W48" s="3"/>
@@ -3613,11 +3582,11 @@
       <c r="AU48" s="3"/>
       <c r="AV48" s="3"/>
     </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="49" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="5" t="s">
         <v>110</v>
       </c>
       <c r="U49" s="3"/>
@@ -3649,13 +3618,31 @@
       <c r="AU49" s="3"/>
       <c r="AV49" s="3"/>
     </row>
-    <row r="50" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="8" t="s">
         <v>112</v>
       </c>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="8"/>
+      <c r="F50" s="8"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="8"/>
+      <c r="I50" s="8"/>
+      <c r="J50" s="8"/>
+      <c r="K50" s="8"/>
+      <c r="L50" s="8"/>
+      <c r="M50" s="8"/>
+      <c r="N50" s="8"/>
+      <c r="O50" s="8"/>
+      <c r="P50" s="8"/>
+      <c r="Q50" s="8"/>
+      <c r="R50" s="8"/>
+      <c r="S50" s="8"/>
+      <c r="T50" s="8"/>
       <c r="U50" s="3"/>
       <c r="V50" s="3"/>
       <c r="W50" s="3"/>
@@ -3685,13 +3672,31 @@
       <c r="AU50" s="3"/>
       <c r="AV50" s="3"/>
     </row>
-    <row r="51" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
+    <row r="51" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="5" t="s">
         <v>114</v>
       </c>
+      <c r="C51" s="8"/>
+      <c r="D51" s="8"/>
+      <c r="E51" s="8"/>
+      <c r="F51" s="8"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="8"/>
+      <c r="I51" s="8"/>
+      <c r="J51" s="8"/>
+      <c r="K51" s="8"/>
+      <c r="L51" s="8"/>
+      <c r="M51" s="8"/>
+      <c r="N51" s="8"/>
+      <c r="O51" s="8"/>
+      <c r="P51" s="8"/>
+      <c r="Q51" s="8"/>
+      <c r="R51" s="8"/>
+      <c r="S51" s="8"/>
+      <c r="T51" s="8"/>
       <c r="U51" s="3"/>
       <c r="V51" s="3"/>
       <c r="W51" s="3"/>
@@ -3721,11 +3726,11 @@
       <c r="AU51" s="3"/>
       <c r="AV51" s="3"/>
     </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="52" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B52" s="8" t="s">
+      <c r="B52" s="5" t="s">
         <v>116</v>
       </c>
       <c r="C52" s="8"/>
@@ -3775,11 +3780,11 @@
       <c r="AU52" s="3"/>
       <c r="AV52" s="3"/>
     </row>
-    <row r="53" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="53" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="5" t="s">
         <v>118</v>
       </c>
       <c r="C53" s="8"/>
@@ -3829,11 +3834,11 @@
       <c r="AU53" s="3"/>
       <c r="AV53" s="3"/>
     </row>
-    <row r="54" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="54" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="5" t="s">
         <v>120</v>
       </c>
       <c r="C54" s="8"/>
@@ -3883,11 +3888,11 @@
       <c r="AU54" s="3"/>
       <c r="AV54" s="3"/>
     </row>
-    <row r="55" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="5" t="s">
         <v>122</v>
       </c>
       <c r="C55" s="8"/>
@@ -3937,11 +3942,11 @@
       <c r="AU55" s="3"/>
       <c r="AV55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="1" t="s">
         <v>124</v>
       </c>
       <c r="C56" s="8"/>
@@ -3991,14 +3996,14 @@
       <c r="AU56" s="3"/>
       <c r="AV56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="57" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="C57" s="8"/>
+      <c r="C57" s="5"/>
       <c r="D57" s="8"/>
       <c r="E57" s="8"/>
       <c r="F57" s="8"/>
@@ -4046,30 +4051,12 @@
       <c r="AV57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="8" t="s">
+      <c r="A58" s="1" t="s">
         <v>127</v>
       </c>
       <c r="B58" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
-      <c r="E58" s="8"/>
-      <c r="F58" s="8"/>
-      <c r="G58" s="8"/>
-      <c r="H58" s="8"/>
-      <c r="I58" s="8"/>
-      <c r="J58" s="8"/>
-      <c r="K58" s="8"/>
-      <c r="L58" s="8"/>
-      <c r="M58" s="8"/>
-      <c r="N58" s="8"/>
-      <c r="O58" s="8"/>
-      <c r="P58" s="8"/>
-      <c r="Q58" s="8"/>
-      <c r="R58" s="8"/>
-      <c r="S58" s="8"/>
-      <c r="T58" s="8"/>
       <c r="U58" s="3"/>
       <c r="V58" s="3"/>
       <c r="W58" s="3"/>
@@ -4099,31 +4086,13 @@
       <c r="AU58" s="3"/>
       <c r="AV58" s="3"/>
     </row>
-    <row r="59" customFormat="false" ht="137.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="8" t="s">
+    <row r="59" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="C59" s="4"/>
-      <c r="D59" s="8"/>
-      <c r="E59" s="8"/>
-      <c r="F59" s="8"/>
-      <c r="G59" s="8"/>
-      <c r="H59" s="8"/>
-      <c r="I59" s="8"/>
-      <c r="J59" s="8"/>
-      <c r="K59" s="8"/>
-      <c r="L59" s="8"/>
-      <c r="M59" s="8"/>
-      <c r="N59" s="8"/>
-      <c r="O59" s="8"/>
-      <c r="P59" s="8"/>
-      <c r="Q59" s="8"/>
-      <c r="R59" s="8"/>
-      <c r="S59" s="8"/>
-      <c r="T59" s="8"/>
       <c r="U59" s="3"/>
       <c r="V59" s="3"/>
       <c r="W59" s="3"/>
@@ -4194,7 +4163,7 @@
         <v>133</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U61" s="3"/>
       <c r="V61" s="3"/>
@@ -4227,10 +4196,10 @@
     </row>
     <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="B62" s="1" t="s">
         <v>135</v>
-      </c>
-      <c r="B62" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="U62" s="3"/>
       <c r="V62" s="3"/>
@@ -4261,12 +4230,12 @@
       <c r="AU62" s="3"/>
       <c r="AV62" s="3"/>
     </row>
-    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B63" s="5" t="s">
         <v>137</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="U63" s="3"/>
       <c r="V63" s="3"/>
@@ -4333,11 +4302,11 @@
       <c r="AU64" s="3"/>
       <c r="AV64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="65" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="1" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="5" t="s">
         <v>141</v>
       </c>
       <c r="U65" s="3"/>
@@ -4374,7 +4343,7 @@
         <v>142</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="U66" s="3"/>
       <c r="V66" s="3"/>
@@ -4405,12 +4374,12 @@
       <c r="AU66" s="3"/>
       <c r="AV66" s="3"/>
     </row>
-    <row r="67" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="67" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>145</v>
+        <v>143</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
@@ -4443,10 +4412,10 @@
     </row>
     <row r="68" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="U68" s="3"/>
       <c r="V68" s="3"/>
@@ -4477,12 +4446,12 @@
       <c r="AU68" s="3"/>
       <c r="AV68" s="3"/>
     </row>
-    <row r="69" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="69" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>146</v>
       </c>
       <c r="U69" s="3"/>
       <c r="V69" s="3"/>
@@ -4515,10 +4484,7 @@
     </row>
     <row r="70" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="U70" s="3"/>
       <c r="V70" s="3"/>
@@ -4549,12 +4515,12 @@
       <c r="AU70" s="3"/>
       <c r="AV70" s="3"/>
     </row>
-    <row r="71" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="71" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B71" s="5" t="s">
         <v>149</v>
-      </c>
-      <c r="B71" s="4" t="s">
-        <v>150</v>
       </c>
       <c r="U71" s="3"/>
       <c r="V71" s="3"/>
@@ -4587,6 +4553,9 @@
     </row>
     <row r="72" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B72" s="1" t="s">
         <v>151</v>
       </c>
       <c r="U72" s="3"/>
@@ -4617,12 +4586,53 @@
       <c r="AT72" s="3"/>
       <c r="AU72" s="3"/>
       <c r="AV72" s="3"/>
-    </row>
-    <row r="73" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY72" s="3"/>
+      <c r="AZ72" s="3"/>
+      <c r="BA72" s="3"/>
+      <c r="BB72" s="3"/>
+      <c r="BC72" s="3"/>
+      <c r="BD72" s="3"/>
+      <c r="BE72" s="3"/>
+      <c r="BF72" s="3"/>
+      <c r="BG72" s="3"/>
+      <c r="BH72" s="3"/>
+      <c r="BI72" s="3"/>
+      <c r="BJ72" s="3"/>
+      <c r="BK72" s="3"/>
+      <c r="BL72" s="3"/>
+      <c r="BM72" s="3"/>
+      <c r="BN72" s="3"/>
+      <c r="BO72" s="3"/>
+      <c r="BP72" s="3"/>
+      <c r="BQ72" s="3"/>
+      <c r="BR72" s="3"/>
+      <c r="BS72" s="3"/>
+      <c r="BT72" s="3"/>
+      <c r="BU72" s="3"/>
+      <c r="BV72" s="3"/>
+      <c r="BW72" s="3"/>
+      <c r="BX72" s="3"/>
+      <c r="BY72" s="3"/>
+      <c r="BZ72" s="3"/>
+      <c r="CA72" s="3"/>
+      <c r="CB72" s="3"/>
+      <c r="CC72" s="3"/>
+      <c r="CD72" s="3"/>
+      <c r="CE72" s="3"/>
+      <c r="CF72" s="3"/>
+      <c r="CG72" s="3"/>
+      <c r="CH72" s="3"/>
+      <c r="CI72" s="3"/>
+      <c r="CJ72" s="3"/>
+      <c r="CK72" s="3"/>
+      <c r="CL72" s="3"/>
+      <c r="CM72" s="3"/>
+    </row>
+    <row r="73" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="1" t="s">
         <v>152</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="1" t="s">
         <v>153</v>
       </c>
       <c r="U73" s="3"/>
@@ -4653,6 +4663,47 @@
       <c r="AT73" s="3"/>
       <c r="AU73" s="3"/>
       <c r="AV73" s="3"/>
+      <c r="AY73" s="3"/>
+      <c r="AZ73" s="3"/>
+      <c r="BA73" s="3"/>
+      <c r="BB73" s="3"/>
+      <c r="BC73" s="3"/>
+      <c r="BD73" s="3"/>
+      <c r="BE73" s="3"/>
+      <c r="BF73" s="3"/>
+      <c r="BG73" s="3"/>
+      <c r="BH73" s="3"/>
+      <c r="BI73" s="3"/>
+      <c r="BJ73" s="3"/>
+      <c r="BK73" s="3"/>
+      <c r="BL73" s="3"/>
+      <c r="BM73" s="3"/>
+      <c r="BN73" s="3"/>
+      <c r="BO73" s="3"/>
+      <c r="BP73" s="3"/>
+      <c r="BQ73" s="3"/>
+      <c r="BR73" s="3"/>
+      <c r="BS73" s="3"/>
+      <c r="BT73" s="3"/>
+      <c r="BU73" s="3"/>
+      <c r="BV73" s="3"/>
+      <c r="BW73" s="3"/>
+      <c r="BX73" s="3"/>
+      <c r="BY73" s="3"/>
+      <c r="BZ73" s="3"/>
+      <c r="CA73" s="3"/>
+      <c r="CB73" s="3"/>
+      <c r="CC73" s="3"/>
+      <c r="CD73" s="3"/>
+      <c r="CE73" s="3"/>
+      <c r="CF73" s="3"/>
+      <c r="CG73" s="3"/>
+      <c r="CH73" s="3"/>
+      <c r="CI73" s="3"/>
+      <c r="CJ73" s="3"/>
+      <c r="CK73" s="3"/>
+      <c r="CL73" s="3"/>
+      <c r="CM73" s="3"/>
     </row>
     <row r="74" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="1" t="s">
@@ -4731,11 +4782,11 @@
       <c r="CL74" s="3"/>
       <c r="CM74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="75" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="5" t="s">
         <v>157</v>
       </c>
       <c r="U75" s="3"/>
@@ -4808,11 +4859,11 @@
       <c r="CL75" s="3"/>
       <c r="CM75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="5" t="s">
         <v>159</v>
       </c>
       <c r="U76" s="3"/>
@@ -4885,11 +4936,11 @@
       <c r="CL76" s="3"/>
       <c r="CM76" s="3"/>
     </row>
-    <row r="77" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="77" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="5" t="s">
         <v>161</v>
       </c>
       <c r="U77" s="3"/>
@@ -4962,11 +5013,11 @@
       <c r="CL77" s="3"/>
       <c r="CM77" s="3"/>
     </row>
-    <row r="78" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="78" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
         <v>162</v>
       </c>
-      <c r="B78" s="4" t="s">
+      <c r="B78" s="5" t="s">
         <v>163</v>
       </c>
       <c r="U78" s="3"/>
@@ -5039,11 +5090,11 @@
       <c r="CL78" s="3"/>
       <c r="CM78" s="3"/>
     </row>
-    <row r="79" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="1" t="s">
         <v>164</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="5" t="s">
         <v>165</v>
       </c>
       <c r="U79" s="3"/>
@@ -5116,11 +5167,11 @@
       <c r="CL79" s="3"/>
       <c r="CM79" s="3"/>
     </row>
-    <row r="80" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="80" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="1" t="s">
         <v>167</v>
       </c>
       <c r="U80" s="3"/>
@@ -5193,11 +5244,11 @@
       <c r="CL80" s="3"/>
       <c r="CM80" s="3"/>
     </row>
-    <row r="81" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="81" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="5" t="s">
         <v>169</v>
       </c>
       <c r="U81" s="3"/>
@@ -5275,7 +5326,7 @@
         <v>170</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
@@ -5347,12 +5398,12 @@
       <c r="CL82" s="3"/>
       <c r="CM82" s="3"/>
     </row>
-    <row r="83" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="83" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>173</v>
+        <v>171</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="U83" s="3"/>
       <c r="V83" s="3"/>
@@ -5426,10 +5477,10 @@
     </row>
     <row r="84" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="U84" s="3"/>
       <c r="V84" s="3"/>
@@ -5503,10 +5554,10 @@
     </row>
     <row r="85" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="U85" s="3"/>
       <c r="V85" s="3"/>
@@ -5580,10 +5631,10 @@
     </row>
     <row r="86" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="1" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="U86" s="3"/>
       <c r="V86" s="3"/>
@@ -5657,10 +5708,10 @@
     </row>
     <row r="87" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B87" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="U87" s="3"/>
       <c r="V87" s="3"/>
@@ -5732,12 +5783,12 @@
       <c r="CL87" s="3"/>
       <c r="CM87" s="3"/>
     </row>
-    <row r="88" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="B88" s="1" t="s">
-        <v>136</v>
+        <v>176</v>
+      </c>
+      <c r="B88" s="5" t="s">
+        <v>177</v>
       </c>
       <c r="U88" s="3"/>
       <c r="V88" s="3"/>
@@ -5811,10 +5862,10 @@
     </row>
     <row r="89" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="B89" s="1" t="s">
         <v>179</v>
-      </c>
-      <c r="B89" s="1" t="s">
-        <v>136</v>
       </c>
       <c r="U89" s="3"/>
       <c r="V89" s="3"/>
@@ -5886,11 +5937,11 @@
       <c r="CL89" s="3"/>
       <c r="CM89" s="3"/>
     </row>
-    <row r="90" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="90" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="5" t="s">
         <v>181</v>
       </c>
       <c r="U90" s="3"/>
@@ -5970,34 +6021,6 @@
       <c r="B91" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="U91" s="3"/>
-      <c r="V91" s="3"/>
-      <c r="W91" s="3"/>
-      <c r="X91" s="3"/>
-      <c r="Y91" s="3"/>
-      <c r="Z91" s="3"/>
-      <c r="AA91" s="3"/>
-      <c r="AB91" s="3"/>
-      <c r="AC91" s="3"/>
-      <c r="AD91" s="3"/>
-      <c r="AE91" s="3"/>
-      <c r="AF91" s="3"/>
-      <c r="AG91" s="3"/>
-      <c r="AH91" s="3"/>
-      <c r="AI91" s="3"/>
-      <c r="AJ91" s="3"/>
-      <c r="AK91" s="3"/>
-      <c r="AL91" s="3"/>
-      <c r="AM91" s="3"/>
-      <c r="AN91" s="3"/>
-      <c r="AO91" s="3"/>
-      <c r="AP91" s="3"/>
-      <c r="AQ91" s="3"/>
-      <c r="AR91" s="3"/>
-      <c r="AS91" s="3"/>
-      <c r="AT91" s="3"/>
-      <c r="AU91" s="3"/>
-      <c r="AV91" s="3"/>
       <c r="AY91" s="3"/>
       <c r="AZ91" s="3"/>
       <c r="BA91" s="3"/>
@@ -6040,41 +6063,13 @@
       <c r="CL91" s="3"/>
       <c r="CM91" s="3"/>
     </row>
-    <row r="92" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B92" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="U92" s="3"/>
-      <c r="V92" s="3"/>
-      <c r="W92" s="3"/>
-      <c r="X92" s="3"/>
-      <c r="Y92" s="3"/>
-      <c r="Z92" s="3"/>
-      <c r="AA92" s="3"/>
-      <c r="AB92" s="3"/>
-      <c r="AC92" s="3"/>
-      <c r="AD92" s="3"/>
-      <c r="AE92" s="3"/>
-      <c r="AF92" s="3"/>
-      <c r="AG92" s="3"/>
-      <c r="AH92" s="3"/>
-      <c r="AI92" s="3"/>
-      <c r="AJ92" s="3"/>
-      <c r="AK92" s="3"/>
-      <c r="AL92" s="3"/>
-      <c r="AM92" s="3"/>
-      <c r="AN92" s="3"/>
-      <c r="AO92" s="3"/>
-      <c r="AP92" s="3"/>
-      <c r="AQ92" s="3"/>
-      <c r="AR92" s="3"/>
-      <c r="AS92" s="3"/>
-      <c r="AT92" s="3"/>
-      <c r="AU92" s="3"/>
-      <c r="AV92" s="3"/>
+      <c r="B92" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="AY92" s="3"/>
       <c r="AZ92" s="3"/>
       <c r="BA92" s="3"/>
@@ -6118,11 +6113,8 @@
       <c r="CM92" s="3"/>
     </row>
     <row r="93" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A93" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="B93" s="1" t="s">
-        <v>187</v>
+      <c r="A93" s="5" t="s">
+        <v>185</v>
       </c>
       <c r="AY93" s="3"/>
       <c r="AZ93" s="3"/>
@@ -6166,12 +6158,12 @@
       <c r="CL93" s="3"/>
       <c r="CM93" s="3"/>
     </row>
-    <row r="94" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="94" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="B94" s="1" t="s">
-        <v>136</v>
+        <v>186</v>
+      </c>
+      <c r="B94" s="5" t="s">
+        <v>187</v>
       </c>
       <c r="AY94" s="3"/>
       <c r="AZ94" s="3"/>
@@ -6216,8 +6208,11 @@
       <c r="CM94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A95" s="4" t="s">
-        <v>189</v>
+      <c r="A95" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>132</v>
       </c>
       <c r="AY95" s="3"/>
       <c r="AZ95" s="3"/>
@@ -6261,12 +6256,12 @@
       <c r="CL95" s="3"/>
       <c r="CM95" s="3"/>
     </row>
-    <row r="96" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="96" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="B96" s="5" t="s">
         <v>190</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>191</v>
       </c>
       <c r="AY96" s="3"/>
       <c r="AZ96" s="3"/>
@@ -6310,13 +6305,31 @@
       <c r="CL96" s="3"/>
       <c r="CM96" s="3"/>
     </row>
-    <row r="97" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A97" s="1" t="s">
+    <row r="97" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B97" s="5" t="s">
         <v>192</v>
       </c>
-      <c r="B97" s="1" t="s">
-        <v>136</v>
-      </c>
+      <c r="C97" s="8"/>
+      <c r="D97" s="8"/>
+      <c r="E97" s="8"/>
+      <c r="F97" s="8"/>
+      <c r="G97" s="8"/>
+      <c r="H97" s="8"/>
+      <c r="I97" s="8"/>
+      <c r="J97" s="8"/>
+      <c r="K97" s="8"/>
+      <c r="L97" s="8"/>
+      <c r="M97" s="8"/>
+      <c r="N97" s="8"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
+      <c r="Q97" s="8"/>
+      <c r="R97" s="8"/>
+      <c r="S97" s="8"/>
+      <c r="T97" s="8"/>
       <c r="AY97" s="3"/>
       <c r="AZ97" s="3"/>
       <c r="BA97" s="3"/>
@@ -6359,11 +6372,11 @@
       <c r="CL97" s="3"/>
       <c r="CM97" s="3"/>
     </row>
-    <row r="98" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="98" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="1" t="s">
         <v>193</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="5" t="s">
         <v>194</v>
       </c>
       <c r="AY98" s="3"/>
@@ -6408,31 +6421,13 @@
       <c r="CL98" s="3"/>
       <c r="CM98" s="3"/>
     </row>
-    <row r="99" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A99" s="8" t="s">
+    <row r="99" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="1" t="s">
         <v>195</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="5" t="s">
         <v>196</v>
       </c>
-      <c r="C99" s="8"/>
-      <c r="D99" s="8"/>
-      <c r="E99" s="8"/>
-      <c r="F99" s="8"/>
-      <c r="G99" s="8"/>
-      <c r="H99" s="8"/>
-      <c r="I99" s="8"/>
-      <c r="J99" s="8"/>
-      <c r="K99" s="8"/>
-      <c r="L99" s="8"/>
-      <c r="M99" s="8"/>
-      <c r="N99" s="8"/>
-      <c r="O99" s="8"/>
-      <c r="P99" s="8"/>
-      <c r="Q99" s="8"/>
-      <c r="R99" s="8"/>
-      <c r="S99" s="8"/>
-      <c r="T99" s="8"/>
       <c r="AY99" s="3"/>
       <c r="AZ99" s="3"/>
       <c r="BA99" s="3"/>
@@ -6475,60 +6470,67 @@
       <c r="CL99" s="3"/>
       <c r="CM99" s="3"/>
     </row>
-    <row r="100" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="100" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="5" t="s">
         <v>198</v>
       </c>
-      <c r="AY100" s="3"/>
-      <c r="AZ100" s="3"/>
-      <c r="BA100" s="3"/>
-      <c r="BB100" s="3"/>
-      <c r="BC100" s="3"/>
-      <c r="BD100" s="3"/>
-      <c r="BE100" s="3"/>
-      <c r="BF100" s="3"/>
-      <c r="BG100" s="3"/>
-      <c r="BH100" s="3"/>
-      <c r="BI100" s="3"/>
-      <c r="BJ100" s="3"/>
-      <c r="BK100" s="3"/>
-      <c r="BL100" s="3"/>
-      <c r="BM100" s="3"/>
-      <c r="BN100" s="3"/>
-      <c r="BO100" s="3"/>
-      <c r="BP100" s="3"/>
-      <c r="BQ100" s="3"/>
-      <c r="BR100" s="3"/>
-      <c r="BS100" s="3"/>
-      <c r="BT100" s="3"/>
-      <c r="BU100" s="3"/>
-      <c r="BV100" s="3"/>
-      <c r="BW100" s="3"/>
-      <c r="BX100" s="3"/>
-      <c r="BY100" s="3"/>
-      <c r="BZ100" s="3"/>
-      <c r="CA100" s="3"/>
-      <c r="CB100" s="3"/>
-      <c r="CC100" s="3"/>
-      <c r="CD100" s="3"/>
-      <c r="CE100" s="3"/>
-      <c r="CF100" s="3"/>
-      <c r="CG100" s="3"/>
-      <c r="CH100" s="3"/>
-      <c r="CI100" s="3"/>
-      <c r="CJ100" s="3"/>
-      <c r="CK100" s="3"/>
-      <c r="CL100" s="3"/>
-      <c r="CM100" s="3"/>
-    </row>
-    <row r="101" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C100" s="1"/>
+      <c r="D100" s="1"/>
+      <c r="E100" s="1"/>
+      <c r="F100" s="1"/>
+      <c r="G100" s="1"/>
+      <c r="H100" s="1"/>
+      <c r="I100" s="1"/>
+      <c r="J100" s="1"/>
+      <c r="K100" s="1"/>
+      <c r="L100" s="1"/>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
+      <c r="Z100" s="1"/>
+      <c r="AA100" s="1"/>
+      <c r="AB100" s="1"/>
+      <c r="AC100" s="1"/>
+      <c r="AD100" s="1"/>
+      <c r="AE100" s="1"/>
+      <c r="AF100" s="1"/>
+      <c r="AG100" s="1"/>
+      <c r="AH100" s="1"/>
+      <c r="AI100" s="1"/>
+      <c r="AJ100" s="1"/>
+      <c r="AK100" s="1"/>
+      <c r="AL100" s="1"/>
+      <c r="AM100" s="1"/>
+      <c r="AN100" s="1"/>
+      <c r="AO100" s="1"/>
+      <c r="AP100" s="1"/>
+      <c r="AQ100" s="1"/>
+      <c r="AR100" s="1"/>
+      <c r="AS100" s="1"/>
+      <c r="AT100" s="1"/>
+      <c r="AU100" s="1"/>
+      <c r="AV100" s="1"/>
+      <c r="AW100" s="1"/>
+      <c r="AX100" s="1"/>
+    </row>
+    <row r="101" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="1" t="s">
         <v>199</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="5" t="s">
         <v>200</v>
       </c>
       <c r="AY101" s="3"/>
@@ -6573,626 +6575,521 @@
       <c r="CL101" s="3"/>
       <c r="CM101" s="3"/>
     </row>
-    <row r="102" s="3" customFormat="true" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="C102" s="1"/>
-      <c r="D102" s="1"/>
-      <c r="E102" s="1"/>
-      <c r="F102" s="1"/>
-      <c r="G102" s="1"/>
-      <c r="H102" s="1"/>
-      <c r="I102" s="1"/>
-      <c r="J102" s="1"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="1"/>
-      <c r="M102" s="1"/>
-      <c r="N102" s="1"/>
-      <c r="O102" s="1"/>
-      <c r="P102" s="1"/>
-      <c r="Q102" s="1"/>
-      <c r="R102" s="1"/>
-      <c r="S102" s="1"/>
-      <c r="T102" s="1"/>
-      <c r="U102" s="1"/>
-      <c r="V102" s="1"/>
-      <c r="W102" s="1"/>
-      <c r="X102" s="1"/>
-      <c r="Y102" s="1"/>
-      <c r="Z102" s="1"/>
-      <c r="AA102" s="1"/>
-      <c r="AB102" s="1"/>
-      <c r="AC102" s="1"/>
-      <c r="AD102" s="1"/>
-      <c r="AE102" s="1"/>
-      <c r="AF102" s="1"/>
-      <c r="AG102" s="1"/>
-      <c r="AH102" s="1"/>
-      <c r="AI102" s="1"/>
-      <c r="AJ102" s="1"/>
-      <c r="AK102" s="1"/>
-      <c r="AL102" s="1"/>
-      <c r="AM102" s="1"/>
-      <c r="AN102" s="1"/>
-      <c r="AO102" s="1"/>
-      <c r="AP102" s="1"/>
-      <c r="AQ102" s="1"/>
-      <c r="AR102" s="1"/>
-      <c r="AS102" s="1"/>
-      <c r="AT102" s="1"/>
-      <c r="AU102" s="1"/>
-      <c r="AV102" s="1"/>
-      <c r="AW102" s="1"/>
-      <c r="AX102" s="1"/>
-    </row>
-    <row r="103" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="AY102" s="3"/>
+      <c r="AZ102" s="3"/>
+      <c r="BA102" s="3"/>
+      <c r="BB102" s="3"/>
+      <c r="BC102" s="3"/>
+      <c r="BD102" s="3"/>
+      <c r="BE102" s="3"/>
+      <c r="BF102" s="3"/>
+      <c r="BG102" s="3"/>
+      <c r="BH102" s="3"/>
+      <c r="BI102" s="3"/>
+      <c r="BJ102" s="3"/>
+      <c r="BK102" s="3"/>
+      <c r="BL102" s="3"/>
+      <c r="BM102" s="3"/>
+      <c r="BN102" s="3"/>
+      <c r="BO102" s="3"/>
+      <c r="BP102" s="3"/>
+      <c r="BQ102" s="3"/>
+      <c r="BR102" s="3"/>
+      <c r="BS102" s="3"/>
+      <c r="BT102" s="3"/>
+      <c r="BU102" s="3"/>
+      <c r="BV102" s="3"/>
+      <c r="BW102" s="3"/>
+      <c r="BX102" s="3"/>
+      <c r="BY102" s="3"/>
+      <c r="BZ102" s="3"/>
+      <c r="CA102" s="3"/>
+      <c r="CB102" s="3"/>
+      <c r="CC102" s="3"/>
+      <c r="CD102" s="3"/>
+      <c r="CE102" s="3"/>
+      <c r="CF102" s="3"/>
+      <c r="CG102" s="3"/>
+      <c r="CH102" s="3"/>
+      <c r="CI102" s="3"/>
+      <c r="CJ102" s="3"/>
+      <c r="CK102" s="3"/>
+      <c r="CL102" s="3"/>
+      <c r="CM102" s="3"/>
+    </row>
+    <row r="103" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="AY103" s="3"/>
-      <c r="AZ103" s="3"/>
-      <c r="BA103" s="3"/>
-      <c r="BB103" s="3"/>
-      <c r="BC103" s="3"/>
-      <c r="BD103" s="3"/>
-      <c r="BE103" s="3"/>
-      <c r="BF103" s="3"/>
-      <c r="BG103" s="3"/>
-      <c r="BH103" s="3"/>
-      <c r="BI103" s="3"/>
-      <c r="BJ103" s="3"/>
-      <c r="BK103" s="3"/>
-      <c r="BL103" s="3"/>
-      <c r="BM103" s="3"/>
-      <c r="BN103" s="3"/>
-      <c r="BO103" s="3"/>
-      <c r="BP103" s="3"/>
-      <c r="BQ103" s="3"/>
-      <c r="BR103" s="3"/>
-      <c r="BS103" s="3"/>
-      <c r="BT103" s="3"/>
-      <c r="BU103" s="3"/>
-      <c r="BV103" s="3"/>
-      <c r="BW103" s="3"/>
-      <c r="BX103" s="3"/>
-      <c r="BY103" s="3"/>
-      <c r="BZ103" s="3"/>
-      <c r="CA103" s="3"/>
-      <c r="CB103" s="3"/>
-      <c r="CC103" s="3"/>
-      <c r="CD103" s="3"/>
-      <c r="CE103" s="3"/>
-      <c r="CF103" s="3"/>
-      <c r="CG103" s="3"/>
-      <c r="CH103" s="3"/>
-      <c r="CI103" s="3"/>
-      <c r="CJ103" s="3"/>
-      <c r="CK103" s="3"/>
-      <c r="CL103" s="3"/>
-      <c r="CM103" s="3"/>
-    </row>
-    <row r="104" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="104" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="1" t="s">
         <v>205</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="AY104" s="3"/>
-      <c r="AZ104" s="3"/>
-      <c r="BA104" s="3"/>
-      <c r="BB104" s="3"/>
-      <c r="BC104" s="3"/>
-      <c r="BD104" s="3"/>
-      <c r="BE104" s="3"/>
-      <c r="BF104" s="3"/>
-      <c r="BG104" s="3"/>
-      <c r="BH104" s="3"/>
-      <c r="BI104" s="3"/>
-      <c r="BJ104" s="3"/>
-      <c r="BK104" s="3"/>
-      <c r="BL104" s="3"/>
-      <c r="BM104" s="3"/>
-      <c r="BN104" s="3"/>
-      <c r="BO104" s="3"/>
-      <c r="BP104" s="3"/>
-      <c r="BQ104" s="3"/>
-      <c r="BR104" s="3"/>
-      <c r="BS104" s="3"/>
-      <c r="BT104" s="3"/>
-      <c r="BU104" s="3"/>
-      <c r="BV104" s="3"/>
-      <c r="BW104" s="3"/>
-      <c r="BX104" s="3"/>
-      <c r="BY104" s="3"/>
-      <c r="BZ104" s="3"/>
-      <c r="CA104" s="3"/>
-      <c r="CB104" s="3"/>
-      <c r="CC104" s="3"/>
-      <c r="CD104" s="3"/>
-      <c r="CE104" s="3"/>
-      <c r="CF104" s="3"/>
-      <c r="CG104" s="3"/>
-      <c r="CH104" s="3"/>
-      <c r="CI104" s="3"/>
-      <c r="CJ104" s="3"/>
-      <c r="CK104" s="3"/>
-      <c r="CL104" s="3"/>
-      <c r="CM104" s="3"/>
-    </row>
-    <row r="105" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A105" s="1" t="s">
+      <c r="C104" s="5"/>
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
+      <c r="S104" s="5"/>
+      <c r="T104" s="5"/>
+    </row>
+    <row r="105" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="4" t="s">
         <v>207</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="5" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="106" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
+      <c r="K105" s="5"/>
+      <c r="L105" s="5"/>
+      <c r="M105" s="5"/>
+      <c r="N105" s="5"/>
+      <c r="O105" s="5"/>
+      <c r="P105" s="5"/>
+      <c r="Q105" s="5"/>
+      <c r="R105" s="5"/>
+      <c r="S105" s="5"/>
+      <c r="T105" s="5"/>
+    </row>
+    <row r="106" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="C106" s="4"/>
-      <c r="D106" s="4"/>
-      <c r="E106" s="4"/>
-      <c r="F106" s="4"/>
-      <c r="G106" s="4"/>
-      <c r="H106" s="4"/>
-      <c r="I106" s="4"/>
-      <c r="J106" s="4"/>
-      <c r="K106" s="4"/>
-      <c r="L106" s="4"/>
-      <c r="M106" s="4"/>
-      <c r="N106" s="4"/>
-      <c r="O106" s="4"/>
-      <c r="P106" s="4"/>
-      <c r="Q106" s="4"/>
-      <c r="R106" s="4"/>
-      <c r="S106" s="4"/>
-      <c r="T106" s="4"/>
-    </row>
-    <row r="107" customFormat="false" ht="231.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A107" s="5" t="s">
+      <c r="C106" s="5"/>
+      <c r="D106" s="5"/>
+      <c r="E106" s="5"/>
+      <c r="F106" s="5"/>
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+      <c r="I106" s="5"/>
+      <c r="J106" s="5"/>
+      <c r="K106" s="5"/>
+      <c r="L106" s="5"/>
+      <c r="M106" s="5"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="5"/>
+      <c r="P106" s="5"/>
+      <c r="Q106" s="5"/>
+      <c r="R106" s="5"/>
+      <c r="S106" s="5"/>
+      <c r="T106" s="5"/>
+    </row>
+    <row r="107" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="C107" s="4"/>
-      <c r="D107" s="4"/>
-      <c r="E107" s="4"/>
-      <c r="F107" s="4"/>
-      <c r="G107" s="4"/>
-      <c r="H107" s="4"/>
-      <c r="I107" s="4"/>
-      <c r="J107" s="4"/>
-      <c r="K107" s="4"/>
-      <c r="L107" s="4"/>
-      <c r="M107" s="4"/>
-      <c r="N107" s="4"/>
-      <c r="O107" s="4"/>
-      <c r="P107" s="4"/>
-      <c r="Q107" s="4"/>
-      <c r="R107" s="4"/>
-      <c r="S107" s="4"/>
-      <c r="T107" s="4"/>
-    </row>
-    <row r="108" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A108" s="1" t="s">
+      <c r="B108" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="B108" s="4" t="s">
+    </row>
+    <row r="109" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="1" t="s">
         <v>214</v>
       </c>
-      <c r="C108" s="4"/>
-      <c r="D108" s="4"/>
-      <c r="E108" s="4"/>
-      <c r="F108" s="4"/>
-      <c r="G108" s="4"/>
-      <c r="H108" s="4"/>
-      <c r="I108" s="4"/>
-      <c r="J108" s="4"/>
-      <c r="K108" s="4"/>
-      <c r="L108" s="4"/>
-      <c r="M108" s="4"/>
-      <c r="N108" s="4"/>
-      <c r="O108" s="4"/>
-      <c r="P108" s="4"/>
-      <c r="Q108" s="4"/>
-      <c r="R108" s="4"/>
-      <c r="S108" s="4"/>
-      <c r="T108" s="4"/>
-    </row>
-    <row r="109" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A109" s="1" t="s">
+      <c r="B109" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="B109" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="110" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="110" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="1" t="s">
         <v>216</v>
       </c>
-      <c r="B110" s="4" t="s">
+      <c r="B110" s="5" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="111" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C110" s="5"/>
+      <c r="D110" s="5"/>
+      <c r="E110" s="5"/>
+      <c r="F110" s="5"/>
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+      <c r="I110" s="5"/>
+      <c r="J110" s="5"/>
+      <c r="K110" s="5"/>
+      <c r="L110" s="5"/>
+      <c r="M110" s="5"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="5"/>
+      <c r="P110" s="5"/>
+      <c r="Q110" s="5"/>
+      <c r="R110" s="5"/>
+      <c r="S110" s="5"/>
+      <c r="T110" s="5"/>
+    </row>
+    <row r="111" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B111" s="4" t="s">
+      <c r="B111" s="5" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="112" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C111" s="5"/>
+      <c r="D111" s="5"/>
+      <c r="E111" s="5"/>
+      <c r="F111" s="5"/>
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+      <c r="I111" s="5"/>
+      <c r="J111" s="5"/>
+      <c r="K111" s="5"/>
+      <c r="L111" s="5"/>
+      <c r="M111" s="5"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="5"/>
+      <c r="P111" s="5"/>
+      <c r="Q111" s="5"/>
+      <c r="R111" s="5"/>
+      <c r="S111" s="5"/>
+      <c r="T111" s="5"/>
+    </row>
+    <row r="112" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="1" t="s">
         <v>220</v>
       </c>
-      <c r="B112" s="4" t="s">
+      <c r="B112" s="5" t="s">
         <v>221</v>
       </c>
-      <c r="C112" s="4"/>
-      <c r="D112" s="4"/>
-      <c r="E112" s="4"/>
-      <c r="F112" s="4"/>
-      <c r="G112" s="4"/>
-      <c r="H112" s="4"/>
-      <c r="I112" s="4"/>
-      <c r="J112" s="4"/>
-      <c r="K112" s="4"/>
-      <c r="L112" s="4"/>
-      <c r="M112" s="4"/>
-      <c r="N112" s="4"/>
-      <c r="O112" s="4"/>
-      <c r="P112" s="4"/>
-      <c r="Q112" s="4"/>
-      <c r="R112" s="4"/>
-      <c r="S112" s="4"/>
-      <c r="T112" s="4"/>
-    </row>
-    <row r="113" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C112" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="D112" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>225</v>
+      </c>
+      <c r="G112" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="H112" s="5" t="s">
+        <v>227</v>
+      </c>
+      <c r="I112" s="5" t="s">
+        <v>228</v>
+      </c>
+      <c r="J112" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="K112" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="L112" s="5" t="s">
+        <v>231</v>
+      </c>
+      <c r="M112" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="N112" s="5" t="s">
+        <v>233</v>
+      </c>
+      <c r="O112" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="P112" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="Q112" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="R112" s="5" t="s">
+        <v>237</v>
+      </c>
+      <c r="S112" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="T112" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="1" t="s">
-        <v>222</v>
-      </c>
-      <c r="B113" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="C113" s="4"/>
-      <c r="D113" s="4"/>
-      <c r="E113" s="4"/>
-      <c r="F113" s="4"/>
-      <c r="G113" s="4"/>
-      <c r="H113" s="4"/>
-      <c r="I113" s="4"/>
-      <c r="J113" s="4"/>
-      <c r="K113" s="4"/>
-      <c r="L113" s="4"/>
-      <c r="M113" s="4"/>
-      <c r="N113" s="4"/>
-      <c r="O113" s="4"/>
-      <c r="P113" s="4"/>
-      <c r="Q113" s="4"/>
-      <c r="R113" s="4"/>
-      <c r="S113" s="4"/>
-      <c r="T113" s="4"/>
-    </row>
-    <row r="114" customFormat="false" ht="74.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>240</v>
+      </c>
+      <c r="B113" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="1" t="s">
-        <v>224</v>
-      </c>
-      <c r="B114" s="4" t="s">
-        <v>225</v>
-      </c>
-      <c r="C114" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="D114" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="E114" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F114" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="G114" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>231</v>
-      </c>
-      <c r="I114" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="J114" s="4" t="s">
-        <v>233</v>
-      </c>
-      <c r="K114" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="L114" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="M114" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="N114" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="O114" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="P114" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="Q114" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="R114" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="S114" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="T114" s="4" t="s">
+      <c r="B114" s="5" t="s">
         <v>243</v>
       </c>
     </row>
-    <row r="115" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A115" s="1" t="s">
+    <row r="115" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="B115" s="4" t="s">
+      <c r="B115" s="5" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="116" customFormat="false" ht="116.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C115" s="8"/>
+      <c r="D115" s="8"/>
+      <c r="E115" s="8"/>
+      <c r="F115" s="8"/>
+      <c r="G115" s="8"/>
+      <c r="H115" s="8"/>
+      <c r="I115" s="8"/>
+      <c r="J115" s="8"/>
+      <c r="K115" s="8"/>
+      <c r="L115" s="8"/>
+      <c r="M115" s="8"/>
+      <c r="N115" s="8"/>
+      <c r="O115" s="8"/>
+      <c r="P115" s="8"/>
+      <c r="Q115" s="8"/>
+      <c r="R115" s="8"/>
+      <c r="S115" s="8"/>
+      <c r="T115" s="8"/>
+    </row>
+    <row r="116" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="B116" s="4" t="s">
+      <c r="B116" s="9" t="s">
         <v>247</v>
       </c>
     </row>
-    <row r="117" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="8" t="s">
+    <row r="117" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="1" t="s">
         <v>248</v>
       </c>
-      <c r="B117" s="4" t="s">
+      <c r="B117" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="C117" s="8"/>
-      <c r="D117" s="8"/>
-      <c r="E117" s="8"/>
-      <c r="F117" s="8"/>
-      <c r="G117" s="8"/>
-      <c r="H117" s="8"/>
-      <c r="I117" s="8"/>
-      <c r="J117" s="8"/>
-      <c r="K117" s="8"/>
-      <c r="L117" s="8"/>
-      <c r="M117" s="8"/>
-      <c r="N117" s="8"/>
-      <c r="O117" s="8"/>
-      <c r="P117" s="8"/>
-      <c r="Q117" s="8"/>
-      <c r="R117" s="8"/>
-      <c r="S117" s="8"/>
-      <c r="T117" s="8"/>
-    </row>
-    <row r="118" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="118" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B118" s="9" t="s">
+      <c r="B118" s="5" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="119" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="119" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="1" t="s">
         <v>252</v>
       </c>
-      <c r="B119" s="9" t="s">
+      <c r="B119" s="1" t="s">
         <v>253</v>
       </c>
-    </row>
-    <row r="120" customFormat="false" ht="85.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="E119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="F119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="G119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="H119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="I119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="J119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="K119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="L119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="M119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="N119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="O119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="P119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="Q119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="R119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="S119" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="T119" s="1" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="1" t="s">
         <v>254</v>
       </c>
-      <c r="B120" s="4" t="s">
+      <c r="B120" s="5" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="121" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="121" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="1" t="s">
         <v>256</v>
       </c>
-      <c r="B121" s="1" t="s">
+      <c r="B121" s="5" t="s">
         <v>257</v>
       </c>
-      <c r="C121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="D121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="F121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="G121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="J121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="O121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="P121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="Q121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="R121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="S121" s="1" t="s">
-        <v>257</v>
-      </c>
-      <c r="T121" s="1" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="122" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    </row>
+    <row r="122" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B122" s="4" t="s">
+      <c r="B122" s="1" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="123" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="123" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="B123" s="4" t="s">
+      <c r="B123" s="1" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="124" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="124" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="B124" s="1" t="s">
+      <c r="B124" s="5" t="s">
         <v>263</v>
       </c>
     </row>
-    <row r="125" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="125" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="1" t="s">
         <v>264</v>
       </c>
-      <c r="B125" s="1" t="s">
+      <c r="B125" s="5" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="126" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="126" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="B126" s="4" t="s">
+      <c r="B126" s="5" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="127" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="127" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="1" t="s">
         <v>268</v>
       </c>
-      <c r="B127" s="4" t="s">
+      <c r="B127" s="5" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="B128" s="4" t="s">
+      <c r="B128" s="5" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="129" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="1" t="s">
         <v>272</v>
       </c>
-      <c r="B129" s="4" t="s">
+      <c r="B129" s="5" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="130" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="130" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="1" t="s">
         <v>274</v>
       </c>
-      <c r="B130" s="4" t="s">
+      <c r="B130" s="5" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="131" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="131" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="B131" s="4" t="s">
+      <c r="B131" s="9" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="132" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="132" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A132" s="1" t="s">
         <v>278</v>
       </c>
-      <c r="B132" s="4" t="s">
+      <c r="B132" s="9" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="133" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="133" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A133" s="1" t="s">
         <v>280</v>
       </c>
-      <c r="B133" s="9" t="s">
+      <c r="B133" s="5" t="s">
         <v>281</v>
       </c>
     </row>
-    <row r="134" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A134" s="1" t="s">
-        <v>282</v>
-      </c>
-      <c r="B134" s="9" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="135" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A135" s="1" t="s">
-        <v>284</v>
-      </c>
-      <c r="B135" s="4" t="s">
-        <v>285</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:T134"/>
+  <autoFilter ref="A2:T132"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
